--- a/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Homeworlds_Production.xlsx
+++ b/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Homeworlds_Production.xlsx
@@ -2,34 +2,34 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R2c7928c2d9454319"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="R4e46e00df42d462b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="Rceacaf4fb82846b6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="R72daf65f43164595"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="R376abf82b7dc453e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="R0c34a6d9aacd47a0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="R2acc67bd7bc74e64"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="R4bca9e224c4d4e3a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="R4f1518effef54e5f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="R0d75789473cf49e8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="R609bcf5a507d4e03"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="R5f850fa9e4ec419c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="R2be5d2ef465d42c0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="R213510c07fa14d17"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="Rfa7446fee37649e2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="Refae6383bbe9480c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="R727c5d4027b54ff9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="Rf10347c263a6403b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="R2e171797a4954b68"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="Rbce8535ce5954553"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="Radb315ba23d1472c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="R8b9ea90d2aaa407f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="R3eb2740a1b15410b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="R27f67c3b82f5481c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="R9e53fce148f3454f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="Rd8174ef137474b08"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="R50ce94dd7000414e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="R0e08306123bd4b13"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R8e53422802774fce"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="R646207d78b404e28"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="Rab0b5360333d48a1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="R64634ba84ab24a35"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="Re589466002ef48e2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="R4fc90e2647184fa3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="R79f54bf3414b4e4c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="R5ca19431a375474a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="Ra40904eef80f4f9f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="R8b2838b4018e4641"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="Rfb81aa8cb889404d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="R64e521bd2833450c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="Rf547d43f90ec490b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="Rc34e971655aa4d6c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="R1dce7d44313748d0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="R3e45aeab48f1483e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="R81375266252c46c6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="R0320136426cc4009"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="R9a4569f6e2094581"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="R0a9fa6a33a0345f5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="R4b78e318068344b7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="R0d07de799420480b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="R40a667ebedb942a5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="R5e507006cc384e66"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="Rfd1aa24535c643b5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="R6d618fdb2e69484b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="R3d12b60b979f4f64"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="R6282d20b65f74f05"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -174,7 +174,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="45">
+  <x:cellXfs count="43">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -230,12 +230,6 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
@@ -2156,7 +2150,7 @@
       <x:c r="A5" s="2" t="str">
         <x:v>Fiches suivies</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:f>SUM(B10:B35)</x:f>
         <x:v>171</x:v>
       </x:c>
@@ -2164,7 +2158,7 @@
       <x:c r="D5" s="2" t="str">
         <x:v>Intégrés</x:v>
       </x:c>
-      <x:c r="E5" s="33" t="n">
+      <x:c r="E5" s="31" t="n">
         <x:f>SUM(E10:F35)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2172,7 +2166,7 @@
       <x:c r="G5" s="2" t="str">
         <x:v>À vérifier</x:v>
       </x:c>
-      <x:c r="H5" s="33" t="n">
+      <x:c r="H5" s="31" t="n">
         <x:f>SUM(H10:H35)</x:f>
         <x:v>29</x:v>
       </x:c>
@@ -2180,7 +2174,7 @@
       <x:c r="J5" s="2" t="str">
         <x:v>Extrapolations</x:v>
       </x:c>
-      <x:c r="K5" s="33" t="n">
+      <x:c r="K5" s="31" t="n">
         <x:f>SUM(I10:I35)</x:f>
         <x:v>136</x:v>
       </x:c>
@@ -2203,7 +2197,7 @@
       <x:c r="M6" s="2"/>
     </x:row>
     <x:row r="7" ht="22" customHeight="1">
-      <x:c r="A7" s="34" t="str">
+      <x:c r="A7" s="32" t="str">
         <x:v>Défini = spécification. Établi = référence documentée. Les colonnes d’adaptation restent des propositions.</x:v>
       </x:c>
       <x:c r="B7" s="2"/>
@@ -2235,95 +2229,95 @@
       <x:c r="M8" s="2"/>
     </x:row>
     <x:row r="9" ht="34" customHeight="1">
-      <x:c r="A9" s="30" t="str">
+      <x:c r="A9" s="28" t="str">
         <x:v>Domaine</x:v>
       </x:c>
-      <x:c r="B9" s="31" t="str">
+      <x:c r="B9" s="29" t="str">
         <x:v>Total</x:v>
       </x:c>
-      <x:c r="C9" s="31" t="str">
+      <x:c r="C9" s="29" t="str">
         <x:v>Défini</x:v>
       </x:c>
-      <x:c r="D9" s="31" t="str">
+      <x:c r="D9" s="29" t="str">
         <x:v>Prototype</x:v>
       </x:c>
-      <x:c r="E9" s="31" t="str">
+      <x:c r="E9" s="29" t="str">
         <x:v>Intégré</x:v>
       </x:c>
-      <x:c r="F9" s="31" t="str">
+      <x:c r="F9" s="29" t="str">
         <x:v>Validé</x:v>
       </x:c>
-      <x:c r="G9" s="31" t="str">
+      <x:c r="G9" s="29" t="str">
         <x:v>Établi</x:v>
       </x:c>
-      <x:c r="H9" s="31" t="str">
+      <x:c r="H9" s="29" t="str">
         <x:v>À vérifier</x:v>
       </x:c>
-      <x:c r="I9" s="31" t="str">
+      <x:c r="I9" s="29" t="str">
         <x:v>Extrapolation</x:v>
       </x:c>
-      <x:c r="J9" s="31" t="str">
+      <x:c r="J9" s="29" t="str">
         <x:v>Coupé attesté</x:v>
       </x:c>
-      <x:c r="K9" s="31" t="str">
+      <x:c r="K9" s="29" t="str">
         <x:v>Concept abandonné</x:v>
       </x:c>
-      <x:c r="L9" s="31" t="str">
+      <x:c r="L9" s="29" t="str">
         <x:v>Allégation écartée</x:v>
       </x:c>
-      <x:c r="M9" s="32" t="str">
+      <x:c r="M9" s="30" t="str">
         <x:v>Priorité P0</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="22" customHeight="1">
-      <x:c r="A10" s="35" t="str">
+      <x:c r="A10" s="33" t="str">
         <x:v>Personnages</x:v>
       </x:c>
-      <x:c r="B10" s="39" t="n">
+      <x:c r="B10" s="37" t="n">
         <x:f>COUNTA('Personnages'!$A$7:$A$11)</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C10" s="39" t="n">
+      <x:c r="C10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$C$7:$C$11,"Défini")</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="D10" s="39" t="n">
+      <x:c r="D10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$C$7:$C$11,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E10" s="39" t="n">
+      <x:c r="E10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$C$7:$C$11,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F10" s="39" t="n">
+      <x:c r="F10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$C$7:$C$11,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G10" s="39" t="n">
+      <x:c r="G10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$D$7:$D$11,"Établi")</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="H10" s="39" t="n">
+      <x:c r="H10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$D$7:$D$11,"À vérifier")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I10" s="39" t="n">
+      <x:c r="I10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$D$7:$D$11,"Extrapolation")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J10" s="39" t="n">
+      <x:c r="J10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$D$7:$D$11,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K10" s="39" t="n">
+      <x:c r="K10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$D$7:$D$11,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L10" s="39" t="n">
+      <x:c r="L10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$D$7:$D$11,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M10" s="39" t="n">
+      <x:c r="M10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$E$7:$E$11,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2332,104 +2326,104 @@
       <x:c r="A11" s="2" t="str">
         <x:v>PNJ</x:v>
       </x:c>
-      <x:c r="B11" s="40" t="n">
+      <x:c r="B11" s="38" t="n">
         <x:f>COUNTA('PNJ'!$A$7:$A$12)</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C11" s="40" t="n">
+      <x:c r="C11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$C$7:$C$12,"Défini")</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="D11" s="40" t="n">
+      <x:c r="D11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$C$7:$C$12,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E11" s="40" t="n">
+      <x:c r="E11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$C$7:$C$12,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F11" s="40" t="n">
+      <x:c r="F11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$C$7:$C$12,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G11" s="40" t="n">
+      <x:c r="G11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$D$7:$D$12,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H11" s="40" t="n">
+      <x:c r="H11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$D$7:$D$12,"À vérifier")</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="I11" s="40" t="n">
+      <x:c r="I11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$D$7:$D$12,"Extrapolation")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J11" s="40" t="n">
+      <x:c r="J11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$D$7:$D$12,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K11" s="40" t="n">
+      <x:c r="K11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$D$7:$D$12,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L11" s="40" t="n">
+      <x:c r="L11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$D$7:$D$12,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M11" s="40" t="n">
+      <x:c r="M11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$E$7:$E$12,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="22" customHeight="1">
-      <x:c r="A12" s="35" t="str">
+      <x:c r="A12" s="33" t="str">
         <x:v>Espèces et factions</x:v>
       </x:c>
-      <x:c r="B12" s="39" t="n">
+      <x:c r="B12" s="37" t="n">
         <x:f>COUNTA('Especes_factions'!$A$7:$A$19)</x:f>
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C12" s="39" t="n">
+      <x:c r="C12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$C$7:$C$19,"Défini")</x:f>
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D12" s="39" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$C$7:$C$19,"Prototype")</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E12" s="39" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$C$7:$C$19,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F12" s="39" t="n">
+      <x:c r="F12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$C$7:$C$19,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G12" s="39" t="n">
+      <x:c r="G12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$D$7:$D$19,"Établi")</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="H12" s="39" t="n">
+      <x:c r="H12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$D$7:$D$19,"À vérifier")</x:f>
         <x:v>11</x:v>
       </x:c>
-      <x:c r="I12" s="39" t="n">
+      <x:c r="I12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$D$7:$D$19,"Extrapolation")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J12" s="39" t="n">
+      <x:c r="J12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$D$7:$D$19,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K12" s="39" t="n">
+      <x:c r="K12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$D$7:$D$19,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L12" s="39" t="n">
+      <x:c r="L12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$D$7:$D$19,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M12" s="39" t="n">
+      <x:c r="M12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$E$7:$E$19,"P0")</x:f>
         <x:v>5</x:v>
       </x:c>
@@ -2438,104 +2432,104 @@
       <x:c r="A13" s="2" t="str">
         <x:v>Mondes</x:v>
       </x:c>
-      <x:c r="B13" s="40" t="n">
+      <x:c r="B13" s="38" t="n">
         <x:f>COUNTA('Mondes'!$A$7:$A$12)</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C13" s="40" t="n">
+      <x:c r="C13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$C$7:$C$12,"Défini")</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="D13" s="40" t="n">
+      <x:c r="D13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$C$7:$C$12,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E13" s="40" t="n">
+      <x:c r="E13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$C$7:$C$12,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F13" s="40" t="n">
+      <x:c r="F13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$C$7:$C$12,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G13" s="40" t="n">
+      <x:c r="G13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$D$7:$D$12,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H13" s="40" t="n">
+      <x:c r="H13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$D$7:$D$12,"À vérifier")</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="I13" s="40" t="n">
+      <x:c r="I13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$D$7:$D$12,"Extrapolation")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J13" s="40" t="n">
+      <x:c r="J13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$D$7:$D$12,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K13" s="40" t="n">
+      <x:c r="K13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$D$7:$D$12,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L13" s="40" t="n">
+      <x:c r="L13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$D$7:$D$12,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M13" s="40" t="n">
+      <x:c r="M13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$E$7:$E$12,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="22" customHeight="1">
-      <x:c r="A14" s="35" t="str">
+      <x:c r="A14" s="33" t="str">
         <x:v>Zones</x:v>
       </x:c>
-      <x:c r="B14" s="39" t="n">
+      <x:c r="B14" s="37" t="n">
         <x:f>COUNTA('Zones'!$A$7:$A$12)</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C14" s="39" t="n">
+      <x:c r="C14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$C$7:$C$12,"Défini")</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="D14" s="39" t="n">
+      <x:c r="D14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$C$7:$C$12,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E14" s="39" t="n">
+      <x:c r="E14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$C$7:$C$12,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F14" s="39" t="n">
+      <x:c r="F14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$C$7:$C$12,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G14" s="39" t="n">
+      <x:c r="G14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$D$7:$D$12,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H14" s="39" t="n">
+      <x:c r="H14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$D$7:$D$12,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I14" s="39" t="n">
+      <x:c r="I14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$D$7:$D$12,"Extrapolation")</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="J14" s="39" t="n">
+      <x:c r="J14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$D$7:$D$12,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K14" s="39" t="n">
+      <x:c r="K14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$D$7:$D$12,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L14" s="39" t="n">
+      <x:c r="L14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$D$7:$D$12,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M14" s="39" t="n">
+      <x:c r="M14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$E$7:$E$12,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2544,104 +2538,104 @@
       <x:c r="A15" s="2" t="str">
         <x:v>Liaisons</x:v>
       </x:c>
-      <x:c r="B15" s="40" t="n">
+      <x:c r="B15" s="38" t="n">
         <x:f>COUNTA('Liaisons'!$A$7:$A$13)</x:f>
         <x:v>7</x:v>
       </x:c>
-      <x:c r="C15" s="40" t="n">
+      <x:c r="C15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$C$7:$C$13,"Défini")</x:f>
         <x:v>7</x:v>
       </x:c>
-      <x:c r="D15" s="40" t="n">
+      <x:c r="D15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$C$7:$C$13,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E15" s="40" t="n">
+      <x:c r="E15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$C$7:$C$13,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F15" s="40" t="n">
+      <x:c r="F15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$C$7:$C$13,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G15" s="40" t="n">
+      <x:c r="G15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$D$7:$D$13,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H15" s="40" t="n">
+      <x:c r="H15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$D$7:$D$13,"À vérifier")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I15" s="40" t="n">
+      <x:c r="I15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$D$7:$D$13,"Extrapolation")</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="J15" s="40" t="n">
+      <x:c r="J15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$D$7:$D$13,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K15" s="40" t="n">
+      <x:c r="K15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$D$7:$D$13,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L15" s="40" t="n">
+      <x:c r="L15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$D$7:$D$13,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M15" s="40" t="n">
+      <x:c r="M15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$E$7:$E$13,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="22" customHeight="1">
-      <x:c r="A16" s="35" t="str">
+      <x:c r="A16" s="33" t="str">
         <x:v>Décors</x:v>
       </x:c>
-      <x:c r="B16" s="39" t="n">
+      <x:c r="B16" s="37" t="n">
         <x:f>COUNTA('Decors'!$A$7:$A$12)</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C16" s="39" t="n">
+      <x:c r="C16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$C$7:$C$12,"Défini")</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="D16" s="39" t="n">
+      <x:c r="D16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$C$7:$C$12,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E16" s="39" t="n">
+      <x:c r="E16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$C$7:$C$12,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F16" s="39" t="n">
+      <x:c r="F16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$C$7:$C$12,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G16" s="39" t="n">
+      <x:c r="G16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$D$7:$D$12,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H16" s="39" t="n">
+      <x:c r="H16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$D$7:$D$12,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I16" s="39" t="n">
+      <x:c r="I16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$D$7:$D$12,"Extrapolation")</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="J16" s="39" t="n">
+      <x:c r="J16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$D$7:$D$12,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K16" s="39" t="n">
+      <x:c r="K16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$D$7:$D$12,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L16" s="39" t="n">
+      <x:c r="L16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$D$7:$D$12,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M16" s="39" t="n">
+      <x:c r="M16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$E$7:$E$12,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2650,104 +2644,104 @@
       <x:c r="A17" s="2" t="str">
         <x:v>Props</x:v>
       </x:c>
-      <x:c r="B17" s="40" t="n">
+      <x:c r="B17" s="38" t="n">
         <x:f>COUNTA('Props'!$A$7:$A$14)</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C17" s="40" t="n">
+      <x:c r="C17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$C$7:$C$14,"Défini")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="D17" s="40" t="n">
+      <x:c r="D17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$C$7:$C$14,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E17" s="40" t="n">
+      <x:c r="E17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$C$7:$C$14,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F17" s="40" t="n">
+      <x:c r="F17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$C$7:$C$14,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G17" s="40" t="n">
+      <x:c r="G17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$D$7:$D$14,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H17" s="40" t="n">
+      <x:c r="H17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$D$7:$D$14,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I17" s="40" t="n">
+      <x:c r="I17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$D$7:$D$14,"Extrapolation")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J17" s="40" t="n">
+      <x:c r="J17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$D$7:$D$14,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K17" s="40" t="n">
+      <x:c r="K17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$D$7:$D$14,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L17" s="40" t="n">
+      <x:c r="L17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$D$7:$D$14,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M17" s="40" t="n">
+      <x:c r="M17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$E$7:$E$14,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="22" customHeight="1">
-      <x:c r="A18" s="35" t="str">
+      <x:c r="A18" s="33" t="str">
         <x:v>Ennemis et boss</x:v>
       </x:c>
-      <x:c r="B18" s="39" t="n">
+      <x:c r="B18" s="37" t="n">
         <x:f>COUNTA('Ennemis_boss'!$A$7:$A$10)</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C18" s="39" t="n">
+      <x:c r="C18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$C$7:$C$10,"Défini")</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D18" s="39" t="n">
+      <x:c r="D18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$C$7:$C$10,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E18" s="39" t="n">
+      <x:c r="E18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$C$7:$C$10,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F18" s="39" t="n">
+      <x:c r="F18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$C$7:$C$10,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G18" s="39" t="n">
+      <x:c r="G18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$D$7:$D$10,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H18" s="39" t="n">
+      <x:c r="H18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$D$7:$D$10,"À vérifier")</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="I18" s="39" t="n">
+      <x:c r="I18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$D$7:$D$10,"Extrapolation")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J18" s="39" t="n">
+      <x:c r="J18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$D$7:$D$10,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K18" s="39" t="n">
+      <x:c r="K18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$D$7:$D$10,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L18" s="39" t="n">
+      <x:c r="L18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$D$7:$D$10,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M18" s="39" t="n">
+      <x:c r="M18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$E$7:$E$10,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2756,104 +2750,104 @@
       <x:c r="A19" s="2" t="str">
         <x:v>Missions</x:v>
       </x:c>
-      <x:c r="B19" s="40" t="n">
+      <x:c r="B19" s="38" t="n">
         <x:f>COUNTA('Missions'!$A$7:$A$14)</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C19" s="40" t="n">
+      <x:c r="C19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$C$7:$C$14,"Défini")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="D19" s="40" t="n">
+      <x:c r="D19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$C$7:$C$14,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E19" s="40" t="n">
+      <x:c r="E19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$C$7:$C$14,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F19" s="40" t="n">
+      <x:c r="F19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$C$7:$C$14,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G19" s="40" t="n">
+      <x:c r="G19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$D$7:$D$14,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H19" s="40" t="n">
+      <x:c r="H19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$D$7:$D$14,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I19" s="40" t="n">
+      <x:c r="I19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$D$7:$D$14,"Extrapolation")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J19" s="40" t="n">
+      <x:c r="J19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$D$7:$D$14,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K19" s="40" t="n">
+      <x:c r="K19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$D$7:$D$14,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L19" s="40" t="n">
+      <x:c r="L19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$D$7:$D$14,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M19" s="40" t="n">
+      <x:c r="M19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$E$7:$E$14,"P0")</x:f>
         <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="22" customHeight="1">
-      <x:c r="A20" s="35" t="str">
+      <x:c r="A20" s="33" t="str">
         <x:v>Secondaires et DLC</x:v>
       </x:c>
-      <x:c r="B20" s="39" t="n">
+      <x:c r="B20" s="37" t="n">
         <x:f>COUNTA('Secondaires_DLC'!$A$7:$A$14)</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C20" s="39" t="n">
+      <x:c r="C20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$C$7:$C$14,"Défini")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="D20" s="39" t="n">
+      <x:c r="D20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$C$7:$C$14,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E20" s="39" t="n">
+      <x:c r="E20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$C$7:$C$14,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F20" s="39" t="n">
+      <x:c r="F20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$C$7:$C$14,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G20" s="39" t="n">
+      <x:c r="G20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$D$7:$D$14,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H20" s="39" t="n">
+      <x:c r="H20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$D$7:$D$14,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I20" s="39" t="n">
+      <x:c r="I20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$D$7:$D$14,"Extrapolation")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J20" s="39" t="n">
+      <x:c r="J20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$D$7:$D$14,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K20" s="39" t="n">
+      <x:c r="K20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$D$7:$D$14,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L20" s="39" t="n">
+      <x:c r="L20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$D$7:$D$14,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M20" s="39" t="n">
+      <x:c r="M20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$E$7:$E$14,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2862,104 +2856,104 @@
       <x:c r="A21" s="2" t="str">
         <x:v>Choix et relations</x:v>
       </x:c>
-      <x:c r="B21" s="40" t="n">
+      <x:c r="B21" s="38" t="n">
         <x:f>COUNTA('Choix_relations'!$A$7:$A$14)</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C21" s="40" t="n">
+      <x:c r="C21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$C$7:$C$14,"Défini")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="D21" s="40" t="n">
+      <x:c r="D21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$C$7:$C$14,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E21" s="40" t="n">
+      <x:c r="E21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$C$7:$C$14,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F21" s="40" t="n">
+      <x:c r="F21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$C$7:$C$14,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G21" s="40" t="n">
+      <x:c r="G21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$D$7:$D$14,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H21" s="40" t="n">
+      <x:c r="H21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$D$7:$D$14,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I21" s="40" t="n">
+      <x:c r="I21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$D$7:$D$14,"Extrapolation")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J21" s="40" t="n">
+      <x:c r="J21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$D$7:$D$14,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K21" s="40" t="n">
+      <x:c r="K21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$D$7:$D$14,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L21" s="40" t="n">
+      <x:c r="L21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$D$7:$D$14,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M21" s="40" t="n">
+      <x:c r="M21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$E$7:$E$14,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="22" customHeight="1">
-      <x:c r="A22" s="35" t="str">
+      <x:c r="A22" s="33" t="str">
         <x:v>Dialogues</x:v>
       </x:c>
-      <x:c r="B22" s="39" t="n">
+      <x:c r="B22" s="37" t="n">
         <x:f>COUNTA('Dialogues'!$A$7:$A$14)</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C22" s="39" t="n">
+      <x:c r="C22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$C$7:$C$14,"Défini")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="D22" s="39" t="n">
+      <x:c r="D22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$C$7:$C$14,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E22" s="39" t="n">
+      <x:c r="E22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$C$7:$C$14,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F22" s="39" t="n">
+      <x:c r="F22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$C$7:$C$14,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G22" s="39" t="n">
+      <x:c r="G22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$D$7:$D$14,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H22" s="39" t="n">
+      <x:c r="H22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$D$7:$D$14,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I22" s="39" t="n">
+      <x:c r="I22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$D$7:$D$14,"Extrapolation")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J22" s="39" t="n">
+      <x:c r="J22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$D$7:$D$14,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K22" s="39" t="n">
+      <x:c r="K22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$D$7:$D$14,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L22" s="39" t="n">
+      <x:c r="L22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$D$7:$D$14,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M22" s="39" t="n">
+      <x:c r="M22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$E$7:$E$14,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2968,104 +2962,104 @@
       <x:c r="A23" s="2" t="str">
         <x:v>Cinématiques</x:v>
       </x:c>
-      <x:c r="B23" s="40" t="n">
+      <x:c r="B23" s="38" t="n">
         <x:f>COUNTA('Cinematiques'!$A$7:$A$14)</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C23" s="40" t="n">
+      <x:c r="C23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$C$7:$C$14,"Défini")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="D23" s="40" t="n">
+      <x:c r="D23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$C$7:$C$14,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E23" s="40" t="n">
+      <x:c r="E23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$C$7:$C$14,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F23" s="40" t="n">
+      <x:c r="F23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$C$7:$C$14,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G23" s="40" t="n">
+      <x:c r="G23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$D$7:$D$14,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H23" s="40" t="n">
+      <x:c r="H23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$D$7:$D$14,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I23" s="40" t="n">
+      <x:c r="I23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$D$7:$D$14,"Extrapolation")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J23" s="40" t="n">
+      <x:c r="J23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$D$7:$D$14,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K23" s="40" t="n">
+      <x:c r="K23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$D$7:$D$14,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L23" s="40" t="n">
+      <x:c r="L23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$D$7:$D$14,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M23" s="40" t="n">
+      <x:c r="M23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$E$7:$E$14,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="22" customHeight="1">
-      <x:c r="A24" s="35" t="str">
+      <x:c r="A24" s="33" t="str">
         <x:v>Armes</x:v>
       </x:c>
-      <x:c r="B24" s="39" t="n">
+      <x:c r="B24" s="37" t="n">
         <x:f>COUNTA('Armes'!$A$7:$A$7)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C24" s="39" t="n">
+      <x:c r="C24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$C$7:$C$7,"Défini")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D24" s="39" t="n">
+      <x:c r="D24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$C$7:$C$7,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E24" s="39" t="n">
+      <x:c r="E24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$C$7:$C$7,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F24" s="39" t="n">
+      <x:c r="F24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$C$7:$C$7,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G24" s="39" t="n">
+      <x:c r="G24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$D$7:$D$7,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H24" s="39" t="n">
+      <x:c r="H24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$D$7:$D$7,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I24" s="39" t="n">
+      <x:c r="I24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$D$7:$D$7,"Extrapolation")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J24" s="39" t="n">
+      <x:c r="J24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$D$7:$D$7,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K24" s="39" t="n">
+      <x:c r="K24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$D$7:$D$7,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L24" s="39" t="n">
+      <x:c r="L24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$D$7:$D$7,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M24" s="39" t="n">
+      <x:c r="M24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$E$7:$E$7,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -3074,104 +3068,104 @@
       <x:c r="A25" s="2" t="str">
         <x:v>Armures et équipement</x:v>
       </x:c>
-      <x:c r="B25" s="40" t="n">
+      <x:c r="B25" s="38" t="n">
         <x:f>COUNTA('Armures_equipement'!$A$7:$A$8)</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C25" s="40" t="n">
+      <x:c r="C25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$C$7:$C$8,"Défini")</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D25" s="40" t="n">
+      <x:c r="D25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$C$7:$C$8,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E25" s="40" t="n">
+      <x:c r="E25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$C$7:$C$8,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F25" s="40" t="n">
+      <x:c r="F25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$C$7:$C$8,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G25" s="40" t="n">
+      <x:c r="G25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$D$7:$D$8,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H25" s="40" t="n">
+      <x:c r="H25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$D$7:$D$8,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I25" s="40" t="n">
+      <x:c r="I25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$D$7:$D$8,"Extrapolation")</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="J25" s="40" t="n">
+      <x:c r="J25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$D$7:$D$8,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K25" s="40" t="n">
+      <x:c r="K25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$D$7:$D$8,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L25" s="40" t="n">
+      <x:c r="L25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$D$7:$D$8,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M25" s="40" t="n">
+      <x:c r="M25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$E$7:$E$8,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="22" customHeight="1">
-      <x:c r="A26" s="35" t="str">
+      <x:c r="A26" s="33" t="str">
         <x:v>Pouvoirs</x:v>
       </x:c>
-      <x:c r="B26" s="39" t="n">
+      <x:c r="B26" s="37" t="n">
         <x:f>COUNTA('Pouvoirs'!$A$7:$A$7)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C26" s="39" t="n">
+      <x:c r="C26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$C$7:$C$7,"Défini")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D26" s="39" t="n">
+      <x:c r="D26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$C$7:$C$7,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E26" s="39" t="n">
+      <x:c r="E26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$C$7:$C$7,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F26" s="39" t="n">
+      <x:c r="F26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$C$7:$C$7,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G26" s="39" t="n">
+      <x:c r="G26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$D$7:$D$7,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H26" s="39" t="n">
+      <x:c r="H26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$D$7:$D$7,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I26" s="39" t="n">
+      <x:c r="I26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$D$7:$D$7,"Extrapolation")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J26" s="39" t="n">
+      <x:c r="J26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$D$7:$D$7,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K26" s="39" t="n">
+      <x:c r="K26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$D$7:$D$7,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L26" s="39" t="n">
+      <x:c r="L26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$D$7:$D$7,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M26" s="39" t="n">
+      <x:c r="M26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$E$7:$E$7,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -3180,104 +3174,104 @@
       <x:c r="A27" s="2" t="str">
         <x:v>Movesets alliés</x:v>
       </x:c>
-      <x:c r="B27" s="40" t="n">
+      <x:c r="B27" s="38" t="n">
         <x:f>COUNTA('Movesets_allies'!$A$7:$A$11)</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C27" s="40" t="n">
+      <x:c r="C27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$C$7:$C$11,"Défini")</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="D27" s="40" t="n">
+      <x:c r="D27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$C$7:$C$11,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E27" s="40" t="n">
+      <x:c r="E27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$C$7:$C$11,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F27" s="40" t="n">
+      <x:c r="F27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$C$7:$C$11,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G27" s="40" t="n">
+      <x:c r="G27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$D$7:$D$11,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H27" s="40" t="n">
+      <x:c r="H27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$D$7:$D$11,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I27" s="40" t="n">
+      <x:c r="I27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$D$7:$D$11,"Extrapolation")</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="J27" s="40" t="n">
+      <x:c r="J27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$D$7:$D$11,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K27" s="40" t="n">
+      <x:c r="K27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$D$7:$D$11,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L27" s="40" t="n">
+      <x:c r="L27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$D$7:$D$11,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M27" s="40" t="n">
+      <x:c r="M27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$E$7:$E$11,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="22" customHeight="1">
-      <x:c r="A28" s="35" t="str">
+      <x:c r="A28" s="33" t="str">
         <x:v>Movesets ennemis</x:v>
       </x:c>
-      <x:c r="B28" s="39" t="n">
+      <x:c r="B28" s="37" t="n">
         <x:f>COUNTA('Movesets_ennemis'!$A$7:$A$14)</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C28" s="39" t="n">
+      <x:c r="C28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$C$7:$C$14,"Défini")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="D28" s="39" t="n">
+      <x:c r="D28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$C$7:$C$14,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E28" s="39" t="n">
+      <x:c r="E28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$C$7:$C$14,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F28" s="39" t="n">
+      <x:c r="F28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$C$7:$C$14,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G28" s="39" t="n">
+      <x:c r="G28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$D$7:$D$14,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H28" s="39" t="n">
+      <x:c r="H28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$D$7:$D$14,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I28" s="39" t="n">
+      <x:c r="I28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$D$7:$D$14,"Extrapolation")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J28" s="39" t="n">
+      <x:c r="J28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$D$7:$D$14,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K28" s="39" t="n">
+      <x:c r="K28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$D$7:$D$14,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L28" s="39" t="n">
+      <x:c r="L28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$D$7:$D$14,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M28" s="39" t="n">
+      <x:c r="M28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$E$7:$E$14,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -3286,104 +3280,104 @@
       <x:c r="A29" s="2" t="str">
         <x:v>Animations</x:v>
       </x:c>
-      <x:c r="B29" s="40" t="n">
+      <x:c r="B29" s="38" t="n">
         <x:f>COUNTA('Animations'!$A$7:$A$17)</x:f>
         <x:v>11</x:v>
       </x:c>
-      <x:c r="C29" s="40" t="n">
+      <x:c r="C29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$C$7:$C$17,"Défini")</x:f>
         <x:v>11</x:v>
       </x:c>
-      <x:c r="D29" s="40" t="n">
+      <x:c r="D29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$C$7:$C$17,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E29" s="40" t="n">
+      <x:c r="E29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$C$7:$C$17,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F29" s="40" t="n">
+      <x:c r="F29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$C$7:$C$17,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G29" s="40" t="n">
+      <x:c r="G29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$D$7:$D$17,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H29" s="40" t="n">
+      <x:c r="H29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$D$7:$D$17,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I29" s="40" t="n">
+      <x:c r="I29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$D$7:$D$17,"Extrapolation")</x:f>
         <x:v>11</x:v>
       </x:c>
-      <x:c r="J29" s="40" t="n">
+      <x:c r="J29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$D$7:$D$17,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K29" s="40" t="n">
+      <x:c r="K29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$D$7:$D$17,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L29" s="40" t="n">
+      <x:c r="L29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$D$7:$D$17,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M29" s="40" t="n">
+      <x:c r="M29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$E$7:$E$17,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="22" customHeight="1">
-      <x:c r="A30" s="35" t="str">
+      <x:c r="A30" s="33" t="str">
         <x:v>Sprites</x:v>
       </x:c>
-      <x:c r="B30" s="39" t="n">
+      <x:c r="B30" s="37" t="n">
         <x:f>COUNTA('Sprites'!$A$7:$A$17)</x:f>
         <x:v>11</x:v>
       </x:c>
-      <x:c r="C30" s="39" t="n">
+      <x:c r="C30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$C$7:$C$17,"Défini")</x:f>
         <x:v>11</x:v>
       </x:c>
-      <x:c r="D30" s="39" t="n">
+      <x:c r="D30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$C$7:$C$17,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E30" s="39" t="n">
+      <x:c r="E30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$C$7:$C$17,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F30" s="39" t="n">
+      <x:c r="F30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$C$7:$C$17,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G30" s="39" t="n">
+      <x:c r="G30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$D$7:$D$17,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H30" s="39" t="n">
+      <x:c r="H30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$D$7:$D$17,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I30" s="39" t="n">
+      <x:c r="I30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$D$7:$D$17,"Extrapolation")</x:f>
         <x:v>11</x:v>
       </x:c>
-      <x:c r="J30" s="39" t="n">
+      <x:c r="J30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$D$7:$D$17,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K30" s="39" t="n">
+      <x:c r="K30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$D$7:$D$17,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L30" s="39" t="n">
+      <x:c r="L30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$D$7:$D$17,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M30" s="39" t="n">
+      <x:c r="M30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$E$7:$E$17,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -3392,104 +3386,104 @@
       <x:c r="A31" s="2" t="str">
         <x:v>VFX</x:v>
       </x:c>
-      <x:c r="B31" s="40" t="n">
+      <x:c r="B31" s="38" t="n">
         <x:f>COUNTA('VFX'!$A$7:$A$14)</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C31" s="40" t="n">
+      <x:c r="C31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$C$7:$C$14,"Défini")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="D31" s="40" t="n">
+      <x:c r="D31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$C$7:$C$14,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E31" s="40" t="n">
+      <x:c r="E31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$C$7:$C$14,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F31" s="40" t="n">
+      <x:c r="F31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$C$7:$C$14,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G31" s="40" t="n">
+      <x:c r="G31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$D$7:$D$14,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H31" s="40" t="n">
+      <x:c r="H31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$D$7:$D$14,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I31" s="40" t="n">
+      <x:c r="I31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$D$7:$D$14,"Extrapolation")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J31" s="40" t="n">
+      <x:c r="J31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$D$7:$D$14,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K31" s="40" t="n">
+      <x:c r="K31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$D$7:$D$14,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L31" s="40" t="n">
+      <x:c r="L31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$D$7:$D$14,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M31" s="40" t="n">
+      <x:c r="M31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$E$7:$E$14,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="22" customHeight="1">
-      <x:c r="A32" s="35" t="str">
+      <x:c r="A32" s="33" t="str">
         <x:v>Audio</x:v>
       </x:c>
-      <x:c r="B32" s="39" t="n">
+      <x:c r="B32" s="37" t="n">
         <x:f>COUNTA('Audio'!$A$7:$A$12)</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C32" s="39" t="n">
+      <x:c r="C32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$C$7:$C$12,"Défini")</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="D32" s="39" t="n">
+      <x:c r="D32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$C$7:$C$12,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E32" s="39" t="n">
+      <x:c r="E32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$C$7:$C$12,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F32" s="39" t="n">
+      <x:c r="F32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$C$7:$C$12,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G32" s="39" t="n">
+      <x:c r="G32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$D$7:$D$12,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H32" s="39" t="n">
+      <x:c r="H32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$D$7:$D$12,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I32" s="39" t="n">
+      <x:c r="I32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$D$7:$D$12,"Extrapolation")</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="J32" s="39" t="n">
+      <x:c r="J32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$D$7:$D$12,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K32" s="39" t="n">
+      <x:c r="K32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$D$7:$D$12,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L32" s="39" t="n">
+      <x:c r="L32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$D$7:$D$12,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M32" s="39" t="n">
+      <x:c r="M32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$E$7:$E$12,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -3498,104 +3492,104 @@
       <x:c r="A33" s="2" t="str">
         <x:v>Systèmes et UI</x:v>
       </x:c>
-      <x:c r="B33" s="40" t="n">
+      <x:c r="B33" s="38" t="n">
         <x:f>COUNTA('UI_systemes'!$A$7:$A$10)</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C33" s="40" t="n">
+      <x:c r="C33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$C$7:$C$10,"Défini")</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D33" s="40" t="n">
+      <x:c r="D33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$C$7:$C$10,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E33" s="40" t="n">
+      <x:c r="E33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$C$7:$C$10,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F33" s="40" t="n">
+      <x:c r="F33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$C$7:$C$10,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G33" s="40" t="n">
+      <x:c r="G33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$D$7:$D$10,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H33" s="40" t="n">
+      <x:c r="H33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$D$7:$D$10,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I33" s="40" t="n">
+      <x:c r="I33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$D$7:$D$10,"Extrapolation")</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="J33" s="40" t="n">
+      <x:c r="J33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$D$7:$D$10,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K33" s="40" t="n">
+      <x:c r="K33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$D$7:$D$10,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L33" s="40" t="n">
+      <x:c r="L33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$D$7:$D$10,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M33" s="40" t="n">
+      <x:c r="M33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$E$7:$E$10,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="22" customHeight="1">
-      <x:c r="A34" s="35" t="str">
+      <x:c r="A34" s="33" t="str">
         <x:v>QA</x:v>
       </x:c>
-      <x:c r="B34" s="39" t="n">
+      <x:c r="B34" s="37" t="n">
         <x:f>COUNTA('QA'!$A$7:$A$17)</x:f>
         <x:v>11</x:v>
       </x:c>
-      <x:c r="C34" s="39" t="n">
+      <x:c r="C34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$C$7:$C$17,"Défini")</x:f>
         <x:v>11</x:v>
       </x:c>
-      <x:c r="D34" s="39" t="n">
+      <x:c r="D34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$C$7:$C$17,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E34" s="39" t="n">
+      <x:c r="E34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$C$7:$C$17,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F34" s="39" t="n">
+      <x:c r="F34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$C$7:$C$17,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G34" s="39" t="n">
+      <x:c r="G34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$D$7:$D$17,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H34" s="39" t="n">
+      <x:c r="H34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$D$7:$D$17,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I34" s="39" t="n">
+      <x:c r="I34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$D$7:$D$17,"Extrapolation")</x:f>
         <x:v>11</x:v>
       </x:c>
-      <x:c r="J34" s="39" t="n">
+      <x:c r="J34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$D$7:$D$17,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K34" s="39" t="n">
+      <x:c r="K34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$D$7:$D$17,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L34" s="39" t="n">
+      <x:c r="L34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$D$7:$D$17,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M34" s="39" t="n">
+      <x:c r="M34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$E$7:$E$17,"P0")</x:f>
         <x:v>11</x:v>
       </x:c>
@@ -3604,119 +3598,119 @@
       <x:c r="A35" s="2" t="str">
         <x:v>Continuité</x:v>
       </x:c>
-      <x:c r="B35" s="40" t="n">
+      <x:c r="B35" s="38" t="n">
         <x:f>COUNTA('Continuite'!$A$7:$A$8)</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C35" s="40" t="n">
+      <x:c r="C35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$C$7:$C$8,"Défini")</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D35" s="40" t="n">
+      <x:c r="D35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$C$7:$C$8,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E35" s="40" t="n">
+      <x:c r="E35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$C$7:$C$8,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F35" s="40" t="n">
+      <x:c r="F35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$C$7:$C$8,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G35" s="40" t="n">
+      <x:c r="G35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$D$7:$D$8,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H35" s="40" t="n">
+      <x:c r="H35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$D$7:$D$8,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I35" s="40" t="n">
+      <x:c r="I35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$D$7:$D$8,"Extrapolation")</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="J35" s="40" t="n">
+      <x:c r="J35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$D$7:$D$8,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K35" s="40" t="n">
+      <x:c r="K35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$D$7:$D$8,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L35" s="40" t="n">
+      <x:c r="L35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$D$7:$D$8,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M35" s="40" t="n">
+      <x:c r="M35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$E$7:$E$8,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="22" customHeight="1">
       <x:c r="A36" s="2"/>
-      <x:c r="B36" s="40"/>
-      <x:c r="C36" s="40"/>
-      <x:c r="D36" s="40"/>
-      <x:c r="E36" s="40"/>
-      <x:c r="F36" s="40"/>
-      <x:c r="G36" s="40"/>
-      <x:c r="H36" s="40"/>
-      <x:c r="I36" s="40"/>
-      <x:c r="J36" s="40"/>
-      <x:c r="K36" s="40"/>
-      <x:c r="L36" s="40"/>
-      <x:c r="M36" s="40"/>
+      <x:c r="B36" s="38"/>
+      <x:c r="C36" s="38"/>
+      <x:c r="D36" s="38"/>
+      <x:c r="E36" s="38"/>
+      <x:c r="F36" s="38"/>
+      <x:c r="G36" s="38"/>
+      <x:c r="H36" s="38"/>
+      <x:c r="I36" s="38"/>
+      <x:c r="J36" s="38"/>
+      <x:c r="K36" s="38"/>
+      <x:c r="L36" s="38"/>
+      <x:c r="M36" s="38"/>
     </x:row>
     <x:row r="37" ht="28" customHeight="1">
-      <x:c r="A37" s="23" t="str">
+      <x:c r="A37" s="21" t="str">
         <x:v>TOTAL</x:v>
       </x:c>
-      <x:c r="B37" s="41" t="n">
+      <x:c r="B37" s="39" t="n">
         <x:f>SUM(B10:B35)</x:f>
         <x:v>171</x:v>
       </x:c>
-      <x:c r="C37" s="41" t="n">
+      <x:c r="C37" s="39" t="n">
         <x:f>SUM(C10:C35)</x:f>
-        <x:v>171</x:v>
-      </x:c>
-      <x:c r="D37" s="41" t="n">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="D37" s="39" t="n">
         <x:f>SUM(D10:D35)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E37" s="41" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E37" s="39" t="n">
         <x:f>SUM(E10:E35)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F37" s="41" t="n">
+      <x:c r="F37" s="39" t="n">
         <x:f>SUM(F10:F35)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G37" s="41" t="n">
+      <x:c r="G37" s="39" t="n">
         <x:f>SUM(G10:G35)</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H37" s="41" t="n">
+      <x:c r="H37" s="39" t="n">
         <x:f>SUM(H10:H35)</x:f>
         <x:v>29</x:v>
       </x:c>
-      <x:c r="I37" s="41" t="n">
+      <x:c r="I37" s="39" t="n">
         <x:f>SUM(I10:I35)</x:f>
         <x:v>136</x:v>
       </x:c>
-      <x:c r="J37" s="41" t="n">
+      <x:c r="J37" s="39" t="n">
         <x:f>SUM(J10:J35)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K37" s="41" t="n">
+      <x:c r="K37" s="39" t="n">
         <x:f>SUM(K10:K35)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L37" s="41" t="n">
+      <x:c r="L37" s="39" t="n">
         <x:f>SUM(L10:L35)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M37" s="41" t="n">
+      <x:c r="M37" s="39" t="n">
         <x:f>SUM(M10:M35)</x:f>
         <x:v>24</x:v>
       </x:c>
@@ -3940,61 +3934,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -4048,10 +4042,10 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>HOM-S-ISSUE1</x:v>
       </x:c>
-      <x:c r="R7" s="20" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect%3A_Homeworlds_1</x:v>
       </x:c>
-      <x:c r="S7" s="20" t="str">
+      <x:c r="S7" s="9" t="str">
         <x:v>L’adversaire ou groupe est attesté selon la source; le combat ATB et ses réglages sont entièrement proposés.</x:v>
       </x:c>
     </x:row>
@@ -4105,10 +4099,10 @@
       <x:c r="Q8" s="7" t="str">
         <x:v>HOM-S-ISSUE2</x:v>
       </x:c>
-      <x:c r="R8" s="21" t="str">
+      <x:c r="R8" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect%3A_Homeworlds_2</x:v>
       </x:c>
-      <x:c r="S8" s="21" t="str">
+      <x:c r="S8" s="7" t="str">
         <x:v>L’adversaire ou groupe est attesté selon la source; le combat ATB et ses réglages sont entièrement proposés.</x:v>
       </x:c>
     </x:row>
@@ -4162,10 +4156,10 @@
       <x:c r="Q9" s="9" t="str">
         <x:v>HOM-S-ISSUE3</x:v>
       </x:c>
-      <x:c r="R9" s="20" t="str">
+      <x:c r="R9" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect%3A_Homeworlds_3</x:v>
       </x:c>
-      <x:c r="S9" s="20" t="str">
+      <x:c r="S9" s="9" t="str">
         <x:v>L’adversaire ou groupe est attesté selon la source; le combat ATB et ses réglages sont entièrement proposés.</x:v>
       </x:c>
     </x:row>
@@ -4219,10 +4213,10 @@
       <x:c r="Q10" s="7" t="str">
         <x:v>HOM-S-ISSUE4</x:v>
       </x:c>
-      <x:c r="R10" s="21" t="str">
+      <x:c r="R10" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect%3A_Homeworlds_4</x:v>
       </x:c>
-      <x:c r="S10" s="21" t="str">
+      <x:c r="S10" s="7" t="str">
         <x:v>L’adversaire ou groupe est attesté selon la source; le combat ATB et ses réglages sont entièrement proposés.</x:v>
       </x:c>
     </x:row>
@@ -4258,7 +4252,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R70b14ec70a57439d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb749c89af65049f0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4398,61 +4392,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -4506,8 +4500,8 @@
         <x:v>Conception originale rattachée à Homeworlds #1</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="68" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -4559,8 +4553,8 @@
         <x:v>Conception originale rattachée à Homeworlds #1</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="68" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -4612,8 +4606,8 @@
         <x:v>Conception originale rattachée à Homeworlds #2</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="68" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -4665,8 +4659,8 @@
         <x:v>Conception originale rattachée à Homeworlds #2</x:v>
       </x:c>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="68" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -4718,8 +4712,8 @@
         <x:v>Conception originale rattachée à Homeworlds #3</x:v>
       </x:c>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="68" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -4771,8 +4765,8 @@
         <x:v>Conception originale rattachée à Homeworlds #3</x:v>
       </x:c>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
     <x:row r="13" ht="68" customHeight="1">
       <x:c r="A13" s="18" t="str">
@@ -4824,8 +4818,8 @@
         <x:v>Conception originale rattachée à Homeworlds #4</x:v>
       </x:c>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str"/>
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str"/>
     </x:row>
     <x:row r="14" ht="68" customHeight="1">
       <x:c r="A14" s="19" t="str">
@@ -4877,8 +4871,8 @@
         <x:v>Conception originale rattachée à Homeworlds #4</x:v>
       </x:c>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str"/>
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D14">
@@ -4912,7 +4906,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R53aa038d22a94377"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R128f389f357a44c8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5052,61 +5046,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -5160,8 +5154,8 @@
         <x:v>Ajout original; cette tâche n’est pas attestée dans le comic.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="68" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -5213,8 +5207,8 @@
         <x:v>Ajout original; cette tâche n’est pas attestée dans le comic.</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="68" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -5266,8 +5260,8 @@
         <x:v>Ajout original; cette tâche n’est pas attestée dans le comic.</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="68" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -5319,8 +5313,8 @@
         <x:v>Ajout original; cette tâche n’est pas attestée dans le comic.</x:v>
       </x:c>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="68" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -5372,8 +5366,8 @@
         <x:v>Ajout original; cette tâche n’est pas attestée dans le comic.</x:v>
       </x:c>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="68" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -5425,8 +5419,8 @@
         <x:v>Ajout original; cette tâche n’est pas attestée dans le comic.</x:v>
       </x:c>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
     <x:row r="13" ht="68" customHeight="1">
       <x:c r="A13" s="18" t="str">
@@ -5478,8 +5472,8 @@
         <x:v>Ajout original; cette tâche n’est pas attestée dans le comic.</x:v>
       </x:c>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str"/>
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str"/>
     </x:row>
     <x:row r="14" ht="68" customHeight="1">
       <x:c r="A14" s="19" t="str">
@@ -5531,8 +5525,8 @@
         <x:v>Ajout original; cette tâche n’est pas attestée dans le comic.</x:v>
       </x:c>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str"/>
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D14">
@@ -5566,7 +5560,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfb4556e139594b12"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R84b65bfdb09e49cb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5706,61 +5700,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -5814,8 +5808,8 @@
         <x:v>Bifurcation de gameplay originale, pas un choix présent dans l’œuvre.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="68" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -5867,8 +5861,8 @@
         <x:v>Bifurcation de gameplay originale, pas un choix présent dans l’œuvre.</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="68" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -5920,8 +5914,8 @@
         <x:v>Bifurcation de gameplay originale, pas un choix présent dans l’œuvre.</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="68" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -5973,8 +5967,8 @@
         <x:v>Bifurcation de gameplay originale, pas un choix présent dans l’œuvre.</x:v>
       </x:c>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="68" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -6026,8 +6020,8 @@
         <x:v>Bifurcation de gameplay originale, pas un choix présent dans l’œuvre.</x:v>
       </x:c>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="68" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -6079,8 +6073,8 @@
         <x:v>Bifurcation de gameplay originale, pas un choix présent dans l’œuvre.</x:v>
       </x:c>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
     <x:row r="13" ht="68" customHeight="1">
       <x:c r="A13" s="18" t="str">
@@ -6132,8 +6126,8 @@
         <x:v>Bifurcation de gameplay originale, pas un choix présent dans l’œuvre.</x:v>
       </x:c>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str"/>
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str"/>
     </x:row>
     <x:row r="14" ht="68" customHeight="1">
       <x:c r="A14" s="19" t="str">
@@ -6185,8 +6179,8 @@
         <x:v>Bifurcation de gameplay originale, pas un choix présent dans l’œuvre.</x:v>
       </x:c>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str"/>
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D14">
@@ -6220,7 +6214,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R79334b86d69344d7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R80d906a83e2e45bc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6360,61 +6354,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -6468,8 +6462,8 @@
         <x:v>Écriture originale à partir des thèmes, sans transcrire les bulles.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="68" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -6521,8 +6515,8 @@
         <x:v>Écriture originale à partir des thèmes, sans transcrire les bulles.</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="68" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -6574,8 +6568,8 @@
         <x:v>Écriture originale à partir des thèmes, sans transcrire les bulles.</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="68" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -6627,8 +6621,8 @@
         <x:v>Écriture originale à partir des thèmes, sans transcrire les bulles.</x:v>
       </x:c>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="68" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -6680,8 +6674,8 @@
         <x:v>Écriture originale à partir des thèmes, sans transcrire les bulles.</x:v>
       </x:c>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="68" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -6733,8 +6727,8 @@
         <x:v>Écriture originale à partir des thèmes, sans transcrire les bulles.</x:v>
       </x:c>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
     <x:row r="13" ht="68" customHeight="1">
       <x:c r="A13" s="18" t="str">
@@ -6786,8 +6780,8 @@
         <x:v>Écriture originale à partir des thèmes, sans transcrire les bulles.</x:v>
       </x:c>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str"/>
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str"/>
     </x:row>
     <x:row r="14" ht="68" customHeight="1">
       <x:c r="A14" s="19" t="str">
@@ -6839,8 +6833,8 @@
         <x:v>Écriture originale à partir des thèmes, sans transcrire les bulles.</x:v>
       </x:c>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str"/>
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D14">
@@ -6874,7 +6868,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R434035ac79504fa6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9506d8d6185a402a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7014,61 +7008,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -7120,8 +7114,8 @@
         <x:v>Découpage original pour sprites 2D sur décor 3D.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="68" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -7171,8 +7165,8 @@
         <x:v>Découpage original pour sprites 2D sur décor 3D.</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="68" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -7222,8 +7216,8 @@
         <x:v>Découpage original pour sprites 2D sur décor 3D.</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="68" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -7273,8 +7267,8 @@
         <x:v>Découpage original pour sprites 2D sur décor 3D.</x:v>
       </x:c>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="68" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -7324,8 +7318,8 @@
         <x:v>Découpage original pour sprites 2D sur décor 3D.</x:v>
       </x:c>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="68" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -7375,8 +7369,8 @@
         <x:v>Découpage original pour sprites 2D sur décor 3D.</x:v>
       </x:c>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
     <x:row r="13" ht="68" customHeight="1">
       <x:c r="A13" s="18" t="str">
@@ -7426,8 +7420,8 @@
         <x:v>Découpage original pour sprites 2D sur décor 3D.</x:v>
       </x:c>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str"/>
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str"/>
     </x:row>
     <x:row r="14" ht="68" customHeight="1">
       <x:c r="A14" s="19" t="str">
@@ -7477,8 +7471,8 @@
         <x:v>Découpage original pour sprites 2D sur décor 3D.</x:v>
       </x:c>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str"/>
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D14">
@@ -7512,7 +7506,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7d2e997beee64483"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R345802746fcc4e44"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7652,61 +7646,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -7758,8 +7752,8 @@
         <x:v>Création de gameplay et direction visuelle originales; modèle exact à vérifier si une arme source est évoquée.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D7">
@@ -7793,7 +7787,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra983175c54a245ba"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4bae463e51574672"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7933,61 +7927,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -8039,8 +8033,8 @@
         <x:v>Création de gameplay et direction visuelle originales; modèle exact à vérifier si une arme source est évoquée.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="68" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -8090,8 +8084,8 @@
         <x:v>Création de gameplay et direction visuelle originales; modèle exact à vérifier si une arme source est évoquée.</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D8">
@@ -8125,7 +8119,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc7ee0951fde647c1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R799d5f5cd841442b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8265,61 +8259,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -8371,8 +8365,8 @@
         <x:v>Création de gameplay et direction visuelle originales; modèle exact à vérifier si une arme source est évoquée.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D7">
@@ -8406,7 +8400,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0bcef596ae334af4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf6693a858c554a43"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8546,61 +8540,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -8654,8 +8648,8 @@
         <x:v>Adaptation originale du rôle; pas un pouvoir officiel du comic.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="68" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -8707,8 +8701,8 @@
         <x:v>Adaptation originale du rôle; pas un pouvoir officiel du comic.</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="68" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -8760,8 +8754,8 @@
         <x:v>Adaptation originale du rôle; pas un pouvoir officiel du comic.</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="68" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -8813,8 +8807,8 @@
         <x:v>Adaptation originale du rôle; pas un pouvoir officiel du comic.</x:v>
       </x:c>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="68" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -8866,8 +8860,8 @@
         <x:v>Adaptation originale du rôle; pas un pouvoir officiel du comic.</x:v>
       </x:c>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D11">
@@ -8901,7 +8895,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R309b0e6710754e7b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcd8c06ff9647497a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9041,61 +9035,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -9149,10 +9143,10 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>HOM-S-BOOK</x:v>
       </x:c>
-      <x:c r="R7" s="20" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://www.penguinrandomhouse.com/books/241700/mass-effect-volume-4-homeworlds-by-mac-walters-various-artists/</x:v>
       </x:c>
-      <x:c r="S7" s="20" t="str">
+      <x:c r="S7" s="9" t="str">
         <x:v>Le rôle dans la source ne prouve ni recrutement jouable ni disponibilité permanente.</x:v>
       </x:c>
     </x:row>
@@ -9206,10 +9200,10 @@
       <x:c r="Q8" s="7" t="str">
         <x:v>HOM-S-BOOK</x:v>
       </x:c>
-      <x:c r="R8" s="21" t="str">
+      <x:c r="R8" s="7" t="str">
         <x:v>https://www.penguinrandomhouse.com/books/241700/mass-effect-volume-4-homeworlds-by-mac-walters-various-artists/</x:v>
       </x:c>
-      <x:c r="S8" s="21" t="str">
+      <x:c r="S8" s="7" t="str">
         <x:v>Le rôle dans la source ne prouve ni recrutement jouable ni disponibilité permanente.</x:v>
       </x:c>
     </x:row>
@@ -9263,10 +9257,10 @@
       <x:c r="Q9" s="9" t="str">
         <x:v>HOM-S-BOOK</x:v>
       </x:c>
-      <x:c r="R9" s="20" t="str">
+      <x:c r="R9" s="9" t="str">
         <x:v>https://www.penguinrandomhouse.com/books/241700/mass-effect-volume-4-homeworlds-by-mac-walters-various-artists/</x:v>
       </x:c>
-      <x:c r="S9" s="20" t="str">
+      <x:c r="S9" s="9" t="str">
         <x:v>Le rôle dans la source ne prouve ni recrutement jouable ni disponibilité permanente.</x:v>
       </x:c>
     </x:row>
@@ -9320,10 +9314,10 @@
       <x:c r="Q10" s="7" t="str">
         <x:v>HOM-S-BOOK</x:v>
       </x:c>
-      <x:c r="R10" s="21" t="str">
+      <x:c r="R10" s="7" t="str">
         <x:v>https://www.penguinrandomhouse.com/books/241700/mass-effect-volume-4-homeworlds-by-mac-walters-various-artists/</x:v>
       </x:c>
-      <x:c r="S10" s="21" t="str">
+      <x:c r="S10" s="7" t="str">
         <x:v>Le rôle dans la source ne prouve ni recrutement jouable ni disponibilité permanente.</x:v>
       </x:c>
     </x:row>
@@ -9377,10 +9371,10 @@
       <x:c r="Q11" s="9" t="str">
         <x:v>HOM-S-ISSUE4</x:v>
       </x:c>
-      <x:c r="R11" s="20" t="str">
+      <x:c r="R11" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect%3A_Homeworlds_4</x:v>
       </x:c>
-      <x:c r="S11" s="20" t="str">
+      <x:c r="S11" s="9" t="str">
         <x:v>Le rôle dans la source ne prouve ni recrutement jouable ni disponibilité permanente.</x:v>
       </x:c>
     </x:row>
@@ -9416,7 +9410,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7845133b2a284750"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R229d5c8be3d54e97"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9556,61 +9550,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -9664,8 +9658,8 @@
         <x:v>Pattern original; pas de valeur numérique canon.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="68" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -9717,8 +9711,8 @@
         <x:v>Pattern original; pas de valeur numérique canon.</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="68" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -9770,8 +9764,8 @@
         <x:v>Pattern original; pas de valeur numérique canon.</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="68" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -9823,8 +9817,8 @@
         <x:v>Pattern original; pas de valeur numérique canon.</x:v>
       </x:c>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="68" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -9876,8 +9870,8 @@
         <x:v>Pattern original; pas de valeur numérique canon.</x:v>
       </x:c>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="68" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -9929,8 +9923,8 @@
         <x:v>Pattern original; pas de valeur numérique canon.</x:v>
       </x:c>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
     <x:row r="13" ht="68" customHeight="1">
       <x:c r="A13" s="18" t="str">
@@ -9982,8 +9976,8 @@
         <x:v>Pattern original; pas de valeur numérique canon.</x:v>
       </x:c>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str"/>
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str"/>
     </x:row>
     <x:row r="14" ht="68" customHeight="1">
       <x:c r="A14" s="19" t="str">
@@ -10035,8 +10029,8 @@
         <x:v>Pattern original; pas de valeur numérique canon.</x:v>
       </x:c>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str"/>
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D14">
@@ -10070,7 +10064,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R88a15f8fe2284596"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R03c64cdbd2ce4cf9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10210,61 +10204,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -10316,8 +10310,8 @@
         <x:v>Conception originale, aucune cadence extraite du comic.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="68" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -10367,8 +10361,8 @@
         <x:v>Conception originale, aucune cadence extraite du comic.</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="68" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -10418,8 +10412,8 @@
         <x:v>Conception originale, aucune cadence extraite du comic.</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="68" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -10469,8 +10463,8 @@
         <x:v>Conception originale, aucune cadence extraite du comic.</x:v>
       </x:c>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="68" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -10520,8 +10514,8 @@
         <x:v>Conception originale, aucune cadence extraite du comic.</x:v>
       </x:c>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="68" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -10571,8 +10565,8 @@
         <x:v>Conception originale, aucune cadence extraite du comic.</x:v>
       </x:c>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
     <x:row r="13" ht="68" customHeight="1">
       <x:c r="A13" s="18" t="str">
@@ -10622,8 +10616,8 @@
         <x:v>Conception originale, aucune cadence extraite du comic.</x:v>
       </x:c>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str"/>
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str"/>
     </x:row>
     <x:row r="14" ht="68" customHeight="1">
       <x:c r="A14" s="19" t="str">
@@ -10673,8 +10667,8 @@
         <x:v>Conception originale, aucune cadence extraite du comic.</x:v>
       </x:c>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str"/>
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str"/>
     </x:row>
     <x:row r="15" ht="68" customHeight="1">
       <x:c r="A15" s="18" t="str">
@@ -10724,8 +10718,8 @@
         <x:v>Conception originale, aucune cadence extraite du comic.</x:v>
       </x:c>
       <x:c r="Q15" s="9" t="str"/>
-      <x:c r="R15" s="20" t="str"/>
-      <x:c r="S15" s="20" t="str"/>
+      <x:c r="R15" s="9" t="str"/>
+      <x:c r="S15" s="9" t="str"/>
     </x:row>
     <x:row r="16" ht="68" customHeight="1">
       <x:c r="A16" s="19" t="str">
@@ -10775,8 +10769,8 @@
         <x:v>Conception originale, aucune cadence extraite du comic.</x:v>
       </x:c>
       <x:c r="Q16" s="7" t="str"/>
-      <x:c r="R16" s="21" t="str"/>
-      <x:c r="S16" s="21" t="str"/>
+      <x:c r="R16" s="7" t="str"/>
+      <x:c r="S16" s="7" t="str"/>
     </x:row>
     <x:row r="17" ht="68" customHeight="1">
       <x:c r="A17" s="18" t="str">
@@ -10826,8 +10820,8 @@
         <x:v>Conception originale, aucune cadence extraite du comic.</x:v>
       </x:c>
       <x:c r="Q17" s="9" t="str"/>
-      <x:c r="R17" s="20" t="str"/>
-      <x:c r="S17" s="20" t="str"/>
+      <x:c r="R17" s="9" t="str"/>
+      <x:c r="S17" s="9" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D17">
@@ -10861,7 +10855,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R364ba81666f04b2a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R714704a35c7f4103"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11001,61 +10995,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -11105,8 +11099,8 @@
         <x:v>Conception originale; référence visuelle du personnage à contrôler.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="68" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -11154,8 +11148,8 @@
         <x:v>Conception originale; référence visuelle du personnage à contrôler.</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="68" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -11203,8 +11197,8 @@
         <x:v>Conception originale; référence visuelle du personnage à contrôler.</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="68" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -11252,8 +11246,8 @@
         <x:v>Conception originale; référence visuelle du personnage à contrôler.</x:v>
       </x:c>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="68" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -11301,8 +11295,8 @@
         <x:v>Conception originale; référence visuelle du personnage à contrôler.</x:v>
       </x:c>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="68" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -11350,8 +11344,8 @@
         <x:v>Conception originale; référence visuelle du personnage à contrôler.</x:v>
       </x:c>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
     <x:row r="13" ht="68" customHeight="1">
       <x:c r="A13" s="18" t="str">
@@ -11399,8 +11393,8 @@
         <x:v>Conception originale; référence visuelle du personnage à contrôler.</x:v>
       </x:c>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str"/>
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str"/>
     </x:row>
     <x:row r="14" ht="68" customHeight="1">
       <x:c r="A14" s="19" t="str">
@@ -11448,8 +11442,8 @@
         <x:v>Conception originale; référence visuelle du personnage à contrôler.</x:v>
       </x:c>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str"/>
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str"/>
     </x:row>
     <x:row r="15" ht="68" customHeight="1">
       <x:c r="A15" s="18" t="str">
@@ -11497,8 +11491,8 @@
         <x:v>Conception originale; référence visuelle du personnage à contrôler.</x:v>
       </x:c>
       <x:c r="Q15" s="9" t="str"/>
-      <x:c r="R15" s="20" t="str"/>
-      <x:c r="S15" s="20" t="str"/>
+      <x:c r="R15" s="9" t="str"/>
+      <x:c r="S15" s="9" t="str"/>
     </x:row>
     <x:row r="16" ht="68" customHeight="1">
       <x:c r="A16" s="19" t="str">
@@ -11546,8 +11540,8 @@
         <x:v>Conception originale; référence visuelle du personnage à contrôler.</x:v>
       </x:c>
       <x:c r="Q16" s="7" t="str"/>
-      <x:c r="R16" s="21" t="str"/>
-      <x:c r="S16" s="21" t="str"/>
+      <x:c r="R16" s="7" t="str"/>
+      <x:c r="S16" s="7" t="str"/>
     </x:row>
     <x:row r="17" ht="68" customHeight="1">
       <x:c r="A17" s="18" t="str">
@@ -11595,8 +11589,8 @@
         <x:v>Conception originale; référence visuelle du personnage à contrôler.</x:v>
       </x:c>
       <x:c r="Q17" s="9" t="str"/>
-      <x:c r="R17" s="20" t="str"/>
-      <x:c r="S17" s="20" t="str"/>
+      <x:c r="R17" s="9" t="str"/>
+      <x:c r="S17" s="9" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D17">
@@ -11630,7 +11624,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0b3ca9804f964cdf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9bbc01f54d9941db"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11770,61 +11764,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -11876,8 +11870,8 @@
         <x:v>VFX original; intensité et timing à régler au prototype.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="68" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -11927,8 +11921,8 @@
         <x:v>VFX original; intensité et timing à régler au prototype.</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="68" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -11978,8 +11972,8 @@
         <x:v>VFX original; intensité et timing à régler au prototype.</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="68" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -12029,8 +12023,8 @@
         <x:v>VFX original; intensité et timing à régler au prototype.</x:v>
       </x:c>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="68" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -12080,8 +12074,8 @@
         <x:v>VFX original; intensité et timing à régler au prototype.</x:v>
       </x:c>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="68" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -12131,8 +12125,8 @@
         <x:v>VFX original; intensité et timing à régler au prototype.</x:v>
       </x:c>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
     <x:row r="13" ht="68" customHeight="1">
       <x:c r="A13" s="18" t="str">
@@ -12182,8 +12176,8 @@
         <x:v>VFX original; intensité et timing à régler au prototype.</x:v>
       </x:c>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str"/>
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str"/>
     </x:row>
     <x:row r="14" ht="68" customHeight="1">
       <x:c r="A14" s="19" t="str">
@@ -12233,8 +12227,8 @@
         <x:v>VFX original; intensité et timing à régler au prototype.</x:v>
       </x:c>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str"/>
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D14">
@@ -12268,7 +12262,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd6fda09635be42c1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3fcb7327c03643a5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12408,61 +12402,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -12516,8 +12510,8 @@
         <x:v>Création sonore originale; aucune piste commerciale requise.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="68" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -12569,8 +12563,8 @@
         <x:v>Création sonore originale; aucune piste commerciale requise.</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="68" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -12622,8 +12616,8 @@
         <x:v>Création sonore originale; aucune piste commerciale requise.</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="68" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -12675,8 +12669,8 @@
         <x:v>Création sonore originale; aucune piste commerciale requise.</x:v>
       </x:c>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="68" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -12728,8 +12722,8 @@
         <x:v>Création sonore originale; aucune piste commerciale requise.</x:v>
       </x:c>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="68" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -12781,8 +12775,8 @@
         <x:v>Création sonore originale; aucune piste commerciale requise.</x:v>
       </x:c>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D12">
@@ -12816,7 +12810,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8f8fb848ef3942ac"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6cee2ce7fb9c4b5e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12956,61 +12950,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -13058,8 +13052,8 @@
         <x:v>Règle originale de production; les ancrages de continuité sont documentés dans les fiches REF.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="68" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -13105,8 +13099,8 @@
         <x:v>Règle originale de production; les ancrages de continuité sont documentés dans les fiches REF.</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="68" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -13152,8 +13146,8 @@
         <x:v>Règle originale de production; les ancrages de continuité sont documentés dans les fiches REF.</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="68" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -13199,8 +13193,8 @@
         <x:v>Règle originale de production; les ancrages de continuité sont documentés dans les fiches REF.</x:v>
       </x:c>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D10">
@@ -13234,7 +13228,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd850005b913041ec"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R54ecc4db11344a67"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13374,61 +13368,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -13476,8 +13470,8 @@
         <x:v>Critère de production original, pas une validation déjà obtenue.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="68" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -13523,8 +13517,8 @@
         <x:v>Critère de production original, pas une validation déjà obtenue.</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="68" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -13570,8 +13564,8 @@
         <x:v>Critère de production original, pas une validation déjà obtenue.</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="68" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -13617,8 +13611,8 @@
         <x:v>Critère de production original, pas une validation déjà obtenue.</x:v>
       </x:c>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="68" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -13664,8 +13658,8 @@
         <x:v>Critère de production original, pas une validation déjà obtenue.</x:v>
       </x:c>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="68" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -13711,8 +13705,8 @@
         <x:v>Critère de production original, pas une validation déjà obtenue.</x:v>
       </x:c>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
     <x:row r="13" ht="68" customHeight="1">
       <x:c r="A13" s="18" t="str">
@@ -13758,8 +13752,8 @@
         <x:v>Critère de production original, pas une validation déjà obtenue.</x:v>
       </x:c>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str"/>
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str"/>
     </x:row>
     <x:row r="14" ht="68" customHeight="1">
       <x:c r="A14" s="19" t="str">
@@ -13805,8 +13799,8 @@
         <x:v>Critère de production original, pas une validation déjà obtenue.</x:v>
       </x:c>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str"/>
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str"/>
     </x:row>
     <x:row r="15" ht="54" customHeight="1">
       <x:c r="A15" s="18" t="str">
@@ -13850,8 +13844,8 @@
         <x:v>Règle originale de production; les ancrages de continuité sont documentés dans les fiches REF.</x:v>
       </x:c>
       <x:c r="Q15" s="9" t="str"/>
-      <x:c r="R15" s="20" t="str"/>
-      <x:c r="S15" s="20" t="str"/>
+      <x:c r="R15" s="9" t="str"/>
+      <x:c r="S15" s="9" t="str"/>
     </x:row>
     <x:row r="16" ht="54" customHeight="1">
       <x:c r="A16" s="19" t="str">
@@ -13895,8 +13889,8 @@
         <x:v>Règle originale de production; les ancrages de continuité sont documentés dans les fiches REF.</x:v>
       </x:c>
       <x:c r="Q16" s="7" t="str"/>
-      <x:c r="R16" s="21" t="str"/>
-      <x:c r="S16" s="21" t="str"/>
+      <x:c r="R16" s="7" t="str"/>
+      <x:c r="S16" s="7" t="str"/>
     </x:row>
     <x:row r="17" ht="68" customHeight="1">
       <x:c r="A17" s="18" t="str">
@@ -13940,8 +13934,8 @@
         <x:v>Règle originale de production; les ancrages de continuité sont documentés dans les fiches REF.</x:v>
       </x:c>
       <x:c r="Q17" s="9" t="str"/>
-      <x:c r="R17" s="20" t="str"/>
-      <x:c r="S17" s="20" t="str"/>
+      <x:c r="R17" s="9" t="str"/>
+      <x:c r="S17" s="9" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D17">
@@ -13975,7 +13969,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1e54f868ca934e80"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfc6920f9dfd5419c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14115,61 +14109,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -14215,8 +14209,8 @@
         <x:v>Règle originale de production; les ancrages de continuité sont documentés dans les fiches REF.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="68" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -14260,8 +14254,8 @@
         <x:v>Règle originale de production; les ancrages de continuité sont documentés dans les fiches REF.</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D8">
@@ -14295,7 +14289,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc02e8be39fed4c6b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R368ed9030ac7463c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14360,10 +14354,10 @@
       <x:c r="F5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Champ</x:v>
       </x:c>
-      <x:c r="B6" s="32" t="str">
+      <x:c r="B6" s="30" t="str">
         <x:v>Définition</x:v>
       </x:c>
       <x:c r="C6" s="2"/>
@@ -14407,12 +14401,12 @@
       <x:c r="E9" s="2"/>
       <x:c r="F9" s="2"/>
     </x:row>
-    <x:row r="10" ht="68" customHeight="1">
+    <x:row r="10" ht="54" customHeight="1">
       <x:c r="A10" s="7" t="str">
         <x:v>Projet</x:v>
       </x:c>
       <x:c r="B10" s="7" t="str">
-        <x:v>Catalogue de quatre modules partageant un cadre de production, avec des règles propres à la fugue urbaine, à la protection d’une preuve, à une défense de position et à la recherche d’archives.</x:v>
+        <x:v>171 fiches de production ; 1 fiches au stade Prototype de portée partielle. Les autres livrables restent des spécifications ; aucun achèvement intégral 1:1 revendiqué.</x:v>
       </x:c>
       <x:c r="C10" s="2"/>
       <x:c r="D10" s="2"/>
@@ -14431,11 +14425,11 @@
       <x:c r="E11" s="2"/>
       <x:c r="F11" s="2"/>
     </x:row>
-    <x:row r="12" ht="40" customHeight="1">
+    <x:row r="12" ht="30" customHeight="1">
       <x:c r="A12" s="7" t="str">
         <x:v>Date de référence</x:v>
       </x:c>
-      <x:c r="B12" s="44" t="d">
+      <x:c r="B12" s="42" t="d">
         <x:v>2026-10-22T12:00:00.000Z</x:v>
       </x:c>
       <x:c r="C12" s="2"/>
@@ -14588,22 +14582,22 @@
       <x:c r="F25" s="2"/>
     </x:row>
     <x:row r="26" ht="34" customHeight="1">
-      <x:c r="A26" s="30" t="str">
+      <x:c r="A26" s="28" t="str">
         <x:v>Source</x:v>
       </x:c>
-      <x:c r="B26" s="31" t="str">
+      <x:c r="B26" s="29" t="str">
         <x:v>Titre</x:v>
       </x:c>
-      <x:c r="C26" s="31" t="str">
+      <x:c r="C26" s="29" t="str">
         <x:v>Type</x:v>
       </x:c>
-      <x:c r="D26" s="31" t="str">
+      <x:c r="D26" s="29" t="str">
         <x:v>URL</x:v>
       </x:c>
-      <x:c r="E26" s="31" t="str">
+      <x:c r="E26" s="29" t="str">
         <x:v>Périmètre</x:v>
       </x:c>
-      <x:c r="F26" s="32" t="str">
+      <x:c r="F26" s="30" t="str">
         <x:v>Accès et limites</x:v>
       </x:c>
     </x:row>
@@ -14752,13 +14746,13 @@
       <x:c r="F35" s="2"/>
     </x:row>
     <x:row r="36" ht="34" customHeight="1">
-      <x:c r="A36" s="30" t="str">
+      <x:c r="A36" s="28" t="str">
         <x:v>Domaine</x:v>
       </x:c>
-      <x:c r="B36" s="31" t="str">
+      <x:c r="B36" s="29" t="str">
         <x:v>Couverture actuelle</x:v>
       </x:c>
-      <x:c r="C36" s="32" t="str">
+      <x:c r="C36" s="30" t="str">
         <x:v>Travail restant</x:v>
       </x:c>
       <x:c r="D36" s="2"/>
@@ -15129,10 +15123,16 @@
       <x:c r="E62" s="2"/>
       <x:c r="F62" s="2"/>
     </x:row>
-    <x:row r="63" ht="22" customHeight="1">
-      <x:c r="A63" s="2"/>
-      <x:c r="B63" s="2"/>
-      <x:c r="C63" s="2"/>
+    <x:row r="63" ht="96" customHeight="1">
+      <x:c r="A63" s="6" t="str">
+        <x:v>Complément lectures contextualisées</x:v>
+      </x:c>
+      <x:c r="B63" s="6" t="str">
+        <x:v>1 références supplémentaires au stade Prototype dans 1 parcours de lecture (1 pages de paraphrases documentaires sourcées), limités à leurs segments exacts.</x:v>
+      </x:c>
+      <x:c r="C63" s="6" t="str">
+        <x:v>Les faits, références, sources et réserves d’origine sont conservés. Ces lectures ne constituent ni un découpage intégral, ni une scène jouable, ni un recrutement ; modèles, voix et animations de l’œuvre ne sont pas produits.</x:v>
+      </x:c>
       <x:c r="D63" s="2"/>
       <x:c r="E63" s="2"/>
       <x:c r="F63" s="2"/>
@@ -15688,6 +15688,14 @@
       <x:c r="D132" s="2"/>
       <x:c r="E132" s="2"/>
       <x:c r="F132" s="2"/>
+    </x:row>
+    <x:row r="133" ht="22" customHeight="1">
+      <x:c r="A133" s="2"/>
+      <x:c r="B133" s="2"/>
+      <x:c r="C133" s="2"/>
+      <x:c r="D133" s="2"/>
+      <x:c r="E133" s="2"/>
+      <x:c r="F133" s="2"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -15829,61 +15837,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -15937,10 +15945,10 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>HOM-S-ISSUE1</x:v>
       </x:c>
-      <x:c r="R7" s="20" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect%3A_Homeworlds_1</x:v>
       </x:c>
-      <x:c r="S7" s="20" t="str">
+      <x:c r="S7" s="9" t="str">
         <x:v>Le rôle dans la source ne prouve ni recrutement jouable ni disponibilité permanente.</x:v>
       </x:c>
     </x:row>
@@ -15994,10 +16002,10 @@
       <x:c r="Q8" s="7" t="str">
         <x:v>HOM-S-ISSUE1</x:v>
       </x:c>
-      <x:c r="R8" s="21" t="str">
+      <x:c r="R8" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect%3A_Homeworlds_1</x:v>
       </x:c>
-      <x:c r="S8" s="21" t="str">
+      <x:c r="S8" s="7" t="str">
         <x:v>Le rôle dans la source ne prouve ni recrutement jouable ni disponibilité permanente.</x:v>
       </x:c>
     </x:row>
@@ -16051,10 +16059,10 @@
       <x:c r="Q9" s="9" t="str">
         <x:v>HOM-S-ISSUE3</x:v>
       </x:c>
-      <x:c r="R9" s="20" t="str">
+      <x:c r="R9" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect%3A_Homeworlds_3</x:v>
       </x:c>
-      <x:c r="S9" s="20" t="str">
+      <x:c r="S9" s="9" t="str">
         <x:v>Le rôle dans la source ne prouve ni recrutement jouable ni disponibilité permanente.</x:v>
       </x:c>
     </x:row>
@@ -16108,10 +16116,10 @@
       <x:c r="Q10" s="7" t="str">
         <x:v>HOM-S-ISSUE3</x:v>
       </x:c>
-      <x:c r="R10" s="21" t="str">
+      <x:c r="R10" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect%3A_Homeworlds_3</x:v>
       </x:c>
-      <x:c r="S10" s="21" t="str">
+      <x:c r="S10" s="7" t="str">
         <x:v>Le rôle dans la source ne prouve ni recrutement jouable ni disponibilité permanente.</x:v>
       </x:c>
     </x:row>
@@ -16165,10 +16173,10 @@
       <x:c r="Q11" s="9" t="str">
         <x:v>HOM-S-ISSUE4</x:v>
       </x:c>
-      <x:c r="R11" s="20" t="str">
+      <x:c r="R11" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect%3A_Homeworlds_4</x:v>
       </x:c>
-      <x:c r="S11" s="20" t="str">
+      <x:c r="S11" s="9" t="str">
         <x:v>Le rôle dans la source ne prouve ni recrutement jouable ni disponibilité permanente.</x:v>
       </x:c>
     </x:row>
@@ -16222,10 +16230,10 @@
       <x:c r="Q12" s="7" t="str">
         <x:v>HOM-S-ISSUE4</x:v>
       </x:c>
-      <x:c r="R12" s="21" t="str">
+      <x:c r="R12" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect%3A_Homeworlds_4</x:v>
       </x:c>
-      <x:c r="S12" s="21" t="str">
+      <x:c r="S12" s="7" t="str">
         <x:v>Le rôle dans la source ne prouve ni recrutement jouable ni disponibilité permanente.</x:v>
       </x:c>
     </x:row>
@@ -16261,7 +16269,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R30dbc8a4e534426c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raf4ad0b70324410c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16288,7 +16296,7 @@
     <x:col min="16" max="16" width="45" hidden="0" customWidth="1"/>
     <x:col min="17" max="17" width="24" hidden="0" customWidth="1"/>
     <x:col min="18" max="18" width="102" hidden="0" customWidth="1"/>
-    <x:col min="19" max="19" width="73" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="255" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="22" customHeight="1">
@@ -16401,61 +16409,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -16501,10 +16509,10 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>HOM-S-BOOK</x:v>
       </x:c>
-      <x:c r="R7" s="20" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://www.penguinrandomhouse.com/books/241700/mass-effect-volume-4-homeworlds-by-mac-walters-various-artists/</x:v>
       </x:c>
-      <x:c r="S7" s="20" t="str">
+      <x:c r="S7" s="9" t="str">
         <x:v>Fait résumé brièvement; aucun dialogue ni découpage intégral du comic reproduit.</x:v>
       </x:c>
     </x:row>
@@ -16550,10 +16558,10 @@
       <x:c r="Q8" s="7" t="str">
         <x:v>HOM-S-ISSUE1</x:v>
       </x:c>
-      <x:c r="R8" s="21" t="str">
+      <x:c r="R8" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect%3A_Homeworlds_1</x:v>
       </x:c>
-      <x:c r="S8" s="21" t="str">
+      <x:c r="S8" s="7" t="str">
         <x:v>Fait résumé brièvement; aucun dialogue ni découpage intégral du comic reproduit.</x:v>
       </x:c>
     </x:row>
@@ -16599,10 +16607,10 @@
       <x:c r="Q9" s="9" t="str">
         <x:v>HOM-S-ISSUE2</x:v>
       </x:c>
-      <x:c r="R9" s="20" t="str">
+      <x:c r="R9" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect%3A_Homeworlds_2</x:v>
       </x:c>
-      <x:c r="S9" s="20" t="str">
+      <x:c r="S9" s="9" t="str">
         <x:v>Fait résumé brièvement; aucun dialogue ni découpage intégral du comic reproduit.</x:v>
       </x:c>
     </x:row>
@@ -16648,14 +16656,14 @@
       <x:c r="Q10" s="7" t="str">
         <x:v>HOM-S-ISSUE3</x:v>
       </x:c>
-      <x:c r="R10" s="21" t="str">
+      <x:c r="R10" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect%3A_Homeworlds_3</x:v>
       </x:c>
-      <x:c r="S10" s="21" t="str">
+      <x:c r="S10" s="7" t="str">
         <x:v>Fait résumé brièvement; aucun dialogue ni découpage intégral du comic reproduit.</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" ht="54" customHeight="1">
+    <x:row r="11" ht="82" customHeight="1">
       <x:c r="A11" s="18" t="str">
         <x:v>HOM-REF-ISSUE4</x:v>
       </x:c>
@@ -16663,7 +16671,7 @@
         <x:v>#4 — Liara T’Soni</x:v>
       </x:c>
       <x:c r="C11" s="15" t="str">
-        <x:v>Défini</x:v>
+        <x:v>Prototype</x:v>
       </x:c>
       <x:c r="D11" s="16" t="str">
         <x:v>Établi</x:v>
@@ -16682,7 +16690,7 @@
       <x:c r="J11" s="9" t="str"/>
       <x:c r="K11" s="9" t="str"/>
       <x:c r="L11" s="9" t="str">
-        <x:v>Livrable proposé : spécification HOM/lore/ref-issue4; brancher au registre de contenu de l'œuvre seulement après production.</x:v>
+        <x:v>Référence documentaire HOM-REF-ISSUE4 consultable dans les lectures hom-liara de src/chronicle-story.js, avec sources et progression séparée. Aucune scène, carte, animation ni incarnation de personnage produite par cette fiche.</x:v>
       </x:c>
       <x:c r="M11" s="9" t="str">
         <x:v>Vérifier toute précision non contenue dans cette notice avant de la déclarer canon.</x:v>
@@ -16697,11 +16705,11 @@
       <x:c r="Q11" s="9" t="str">
         <x:v>HOM-S-DH4</x:v>
       </x:c>
-      <x:c r="R11" s="20" t="str">
+      <x:c r="R11" s="9" t="str">
         <x:v>https://www.darkhorse.com/Comics/21-313/Mass-Effect-Homeworlds-4-Mike-Hawthorne-variant-cover</x:v>
       </x:c>
-      <x:c r="S11" s="20" t="str">
-        <x:v>Fait résumé brièvement; aucun dialogue ni découpage intégral du comic reproduit.</x:v>
+      <x:c r="S11" s="9" t="str">
+        <x:v>Fait résumé brièvement; aucun dialogue ni découpage intégral du comic reproduit. Prototype limité à une paraphrase documentaire sourcée et aux références visitées ; pas de reproduction intégrale du récit. Une lecture n’accorde ni recrutement, équipement, victoire ni récompense de campagne.</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="68" customHeight="1">
@@ -16746,10 +16754,10 @@
       <x:c r="Q12" s="7" t="str">
         <x:v>HOM-S-ISSUE1</x:v>
       </x:c>
-      <x:c r="R12" s="21" t="str">
+      <x:c r="R12" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect%3A_Homeworlds_1</x:v>
       </x:c>
-      <x:c r="S12" s="21" t="str">
+      <x:c r="S12" s="7" t="str">
         <x:v>Ne remplace pas la lecture du numéro.</x:v>
       </x:c>
     </x:row>
@@ -16795,10 +16803,10 @@
       <x:c r="Q13" s="9" t="str">
         <x:v>HOM-S-ISSUE1</x:v>
       </x:c>
-      <x:c r="R13" s="20" t="str">
+      <x:c r="R13" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect%3A_Homeworlds_1</x:v>
       </x:c>
-      <x:c r="S13" s="20" t="str">
+      <x:c r="S13" s="9" t="str">
         <x:v>Ne remplace pas la lecture du numéro.</x:v>
       </x:c>
     </x:row>
@@ -16844,10 +16852,10 @@
       <x:c r="Q14" s="7" t="str">
         <x:v>HOM-S-ISSUE2</x:v>
       </x:c>
-      <x:c r="R14" s="21" t="str">
+      <x:c r="R14" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect%3A_Homeworlds_2</x:v>
       </x:c>
-      <x:c r="S14" s="21" t="str">
+      <x:c r="S14" s="7" t="str">
         <x:v>Ne remplace pas la lecture du numéro.</x:v>
       </x:c>
     </x:row>
@@ -16893,10 +16901,10 @@
       <x:c r="Q15" s="9" t="str">
         <x:v>HOM-S-ISSUE2</x:v>
       </x:c>
-      <x:c r="R15" s="20" t="str">
+      <x:c r="R15" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect%3A_Homeworlds_2</x:v>
       </x:c>
-      <x:c r="S15" s="20" t="str">
+      <x:c r="S15" s="9" t="str">
         <x:v>Ne remplace pas la lecture du numéro.</x:v>
       </x:c>
     </x:row>
@@ -16942,10 +16950,10 @@
       <x:c r="Q16" s="7" t="str">
         <x:v>HOM-S-ISSUE3</x:v>
       </x:c>
-      <x:c r="R16" s="21" t="str">
+      <x:c r="R16" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect%3A_Homeworlds_3</x:v>
       </x:c>
-      <x:c r="S16" s="21" t="str">
+      <x:c r="S16" s="7" t="str">
         <x:v>Ne remplace pas la lecture du numéro.</x:v>
       </x:c>
     </x:row>
@@ -16991,10 +16999,10 @@
       <x:c r="Q17" s="9" t="str">
         <x:v>HOM-S-ISSUE3</x:v>
       </x:c>
-      <x:c r="R17" s="20" t="str">
+      <x:c r="R17" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect%3A_Homeworlds_3</x:v>
       </x:c>
-      <x:c r="S17" s="20" t="str">
+      <x:c r="S17" s="9" t="str">
         <x:v>Ne remplace pas la lecture du numéro.</x:v>
       </x:c>
     </x:row>
@@ -17040,10 +17048,10 @@
       <x:c r="Q18" s="7" t="str">
         <x:v>HOM-S-ISSUE4</x:v>
       </x:c>
-      <x:c r="R18" s="21" t="str">
+      <x:c r="R18" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect%3A_Homeworlds_4</x:v>
       </x:c>
-      <x:c r="S18" s="21" t="str">
+      <x:c r="S18" s="7" t="str">
         <x:v>Ne remplace pas la lecture du numéro.</x:v>
       </x:c>
     </x:row>
@@ -17089,10 +17097,10 @@
       <x:c r="Q19" s="9" t="str">
         <x:v>HOM-S-ISSUE4</x:v>
       </x:c>
-      <x:c r="R19" s="20" t="str">
+      <x:c r="R19" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect%3A_Homeworlds_4</x:v>
       </x:c>
-      <x:c r="S19" s="20" t="str">
+      <x:c r="S19" s="9" t="str">
         <x:v>Ne remplace pas la lecture du numéro.</x:v>
       </x:c>
     </x:row>
@@ -17128,7 +17136,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5d4a8cf5c2cb4436"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2a2b368e8e9c43ce"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17268,61 +17276,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -17370,10 +17378,10 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>HOM-S-ISSUE1</x:v>
       </x:c>
-      <x:c r="R7" s="20" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect%3A_Homeworlds_1</x:v>
       </x:c>
-      <x:c r="S7" s="20" t="str">
+      <x:c r="S7" s="9" t="str">
         <x:v>La géométrie jouable ci-dessous est originale et ne prétend pas reconstituer une carte officielle.</x:v>
       </x:c>
     </x:row>
@@ -17421,10 +17429,10 @@
       <x:c r="Q8" s="7" t="str">
         <x:v>HOM-S-ISSUE1</x:v>
       </x:c>
-      <x:c r="R8" s="21" t="str">
+      <x:c r="R8" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect%3A_Homeworlds_1</x:v>
       </x:c>
-      <x:c r="S8" s="21" t="str">
+      <x:c r="S8" s="7" t="str">
         <x:v>La présence dans #2 est également attestée par ISSUE2; la géométrie commune est une proposition technique.</x:v>
       </x:c>
     </x:row>
@@ -17472,10 +17480,10 @@
       <x:c r="Q9" s="9" t="str">
         <x:v>HOM-S-ISSUE3</x:v>
       </x:c>
-      <x:c r="R9" s="20" t="str">
+      <x:c r="R9" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect%3A_Homeworlds_3</x:v>
       </x:c>
-      <x:c r="S9" s="20" t="str">
+      <x:c r="S9" s="9" t="str">
         <x:v>La géométrie jouable ci-dessous est originale et ne prétend pas reconstituer une carte officielle.</x:v>
       </x:c>
     </x:row>
@@ -17523,10 +17531,10 @@
       <x:c r="Q10" s="7" t="str">
         <x:v>HOM-S-ISSUE3</x:v>
       </x:c>
-      <x:c r="R10" s="21" t="str">
+      <x:c r="R10" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect%3A_Homeworlds_3</x:v>
       </x:c>
-      <x:c r="S10" s="21" t="str">
+      <x:c r="S10" s="7" t="str">
         <x:v>La géométrie jouable ci-dessous est originale et ne prétend pas reconstituer une carte officielle.</x:v>
       </x:c>
     </x:row>
@@ -17574,10 +17582,10 @@
       <x:c r="Q11" s="9" t="str">
         <x:v>HOM-S-ISSUE4</x:v>
       </x:c>
-      <x:c r="R11" s="20" t="str">
+      <x:c r="R11" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect%3A_Homeworlds_4</x:v>
       </x:c>
-      <x:c r="S11" s="20" t="str">
+      <x:c r="S11" s="9" t="str">
         <x:v>La géométrie jouable ci-dessous est originale et ne prétend pas reconstituer une carte officielle.</x:v>
       </x:c>
     </x:row>
@@ -17625,10 +17633,10 @@
       <x:c r="Q12" s="7" t="str">
         <x:v>HOM-S-ISSUE4</x:v>
       </x:c>
-      <x:c r="R12" s="21" t="str">
+      <x:c r="R12" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect%3A_Homeworlds_4</x:v>
       </x:c>
-      <x:c r="S12" s="21" t="str">
+      <x:c r="S12" s="7" t="str">
         <x:v>La géométrie jouable ci-dessous est originale et ne prétend pas reconstituer une carte officielle.</x:v>
       </x:c>
     </x:row>
@@ -17664,7 +17672,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rce373c389c694076"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re2ec94900daf43e9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17804,61 +17812,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -17910,8 +17918,8 @@
         <x:v>Plan original, dimensions à prototyper.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="68" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -17961,8 +17969,8 @@
         <x:v>Plan original, dimensions à prototyper.</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="68" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -18012,8 +18020,8 @@
         <x:v>Plan original, dimensions à prototyper.</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="68" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -18063,8 +18071,8 @@
         <x:v>Plan original, dimensions à prototyper.</x:v>
       </x:c>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="68" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -18114,8 +18122,8 @@
         <x:v>Plan original, dimensions à prototyper.</x:v>
       </x:c>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="68" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -18165,8 +18173,8 @@
         <x:v>Plan original, dimensions à prototyper.</x:v>
       </x:c>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D12">
@@ -18200,7 +18208,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R415c4ff190124d5f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf32b81a9e8214eb4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18340,61 +18348,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -18444,8 +18452,8 @@
         <x:v>Raccord de gameplay original; ordre narratif selon les ancrages sourcés.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="68" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -18493,8 +18501,8 @@
         <x:v>Raccord de gameplay original; ordre narratif selon les ancrages sourcés.</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="68" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -18542,8 +18550,8 @@
         <x:v>Raccord de gameplay original; ordre narratif selon les ancrages sourcés.</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="68" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -18591,8 +18599,8 @@
         <x:v>Raccord de gameplay original; ordre narratif selon les ancrages sourcés.</x:v>
       </x:c>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="68" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -18640,8 +18648,8 @@
         <x:v>Raccord de gameplay original; ordre narratif selon les ancrages sourcés.</x:v>
       </x:c>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="68" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -18689,8 +18697,8 @@
         <x:v>Raccord de gameplay original; ordre narratif selon les ancrages sourcés.</x:v>
       </x:c>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
     <x:row r="13" ht="54" customHeight="1">
       <x:c r="A13" s="18" t="str">
@@ -18736,10 +18744,10 @@
       <x:c r="Q13" s="9" t="str">
         <x:v>HOM-S-ISSUE4</x:v>
       </x:c>
-      <x:c r="R13" s="20" t="str">
+      <x:c r="R13" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect%3A_Homeworlds_4</x:v>
       </x:c>
-      <x:c r="S13" s="20" t="str"/>
+      <x:c r="S13" s="9" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D13">
@@ -18773,7 +18781,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2bac052d92df4b95"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rab651b8ee1ef459c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18913,61 +18921,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -19017,8 +19025,8 @@
         <x:v>Direction artistique originale, matériaux à confronter aux planches.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="68" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -19066,8 +19074,8 @@
         <x:v>Direction artistique originale, matériaux à confronter aux planches.</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="68" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -19115,8 +19123,8 @@
         <x:v>Direction artistique originale, matériaux à confronter aux planches.</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="68" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -19164,8 +19172,8 @@
         <x:v>Direction artistique originale, matériaux à confronter aux planches.</x:v>
       </x:c>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="68" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -19213,8 +19221,8 @@
         <x:v>Direction artistique originale, matériaux à confronter aux planches.</x:v>
       </x:c>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="68" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -19262,8 +19270,8 @@
         <x:v>Direction artistique originale, matériaux à confronter aux planches.</x:v>
       </x:c>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D12">
@@ -19297,7 +19305,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rec54ea812a9c4c68"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdd2d556c81e74f7a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -19437,61 +19445,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -19545,8 +19553,8 @@
         <x:v>Accessoire ou interaction de production proposé; ne vaut pas relevé exhaustif de la planche.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="68" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -19598,8 +19606,8 @@
         <x:v>Accessoire ou interaction de production proposé; ne vaut pas relevé exhaustif de la planche.</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="68" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -19651,8 +19659,8 @@
         <x:v>Accessoire ou interaction de production proposé; ne vaut pas relevé exhaustif de la planche.</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="68" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -19704,8 +19712,8 @@
         <x:v>Accessoire ou interaction de production proposé; ne vaut pas relevé exhaustif de la planche.</x:v>
       </x:c>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="68" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -19757,8 +19765,8 @@
         <x:v>Accessoire ou interaction de production proposé; ne vaut pas relevé exhaustif de la planche.</x:v>
       </x:c>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="68" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -19810,8 +19818,8 @@
         <x:v>Accessoire ou interaction de production proposé; ne vaut pas relevé exhaustif de la planche.</x:v>
       </x:c>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
     <x:row r="13" ht="68" customHeight="1">
       <x:c r="A13" s="18" t="str">
@@ -19863,8 +19871,8 @@
         <x:v>Accessoire ou interaction de production proposé; ne vaut pas relevé exhaustif de la planche.</x:v>
       </x:c>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str"/>
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str"/>
     </x:row>
     <x:row r="14" ht="68" customHeight="1">
       <x:c r="A14" s="19" t="str">
@@ -19916,8 +19924,8 @@
         <x:v>Accessoire ou interaction de production proposé; ne vaut pas relevé exhaustif de la planche.</x:v>
       </x:c>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str"/>
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D14">
@@ -19951,7 +19959,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R14252edcc9e74289"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9639c82b2f164bd9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Homeworlds_Production.xlsx
+++ b/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Homeworlds_Production.xlsx
@@ -2,34 +2,34 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R8e53422802774fce"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="R646207d78b404e28"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="Rab0b5360333d48a1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="R64634ba84ab24a35"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="Re589466002ef48e2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="R4fc90e2647184fa3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="R79f54bf3414b4e4c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="R5ca19431a375474a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="Ra40904eef80f4f9f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="R8b2838b4018e4641"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="Rfb81aa8cb889404d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="R64e521bd2833450c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="Rf547d43f90ec490b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="Rc34e971655aa4d6c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="R1dce7d44313748d0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="R3e45aeab48f1483e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="R81375266252c46c6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="R0320136426cc4009"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="R9a4569f6e2094581"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="R0a9fa6a33a0345f5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="R4b78e318068344b7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="R0d07de799420480b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="R40a667ebedb942a5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="R5e507006cc384e66"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="Rfd1aa24535c643b5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="R6d618fdb2e69484b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="R3d12b60b979f4f64"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="R6282d20b65f74f05"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R5b68e7d1b8c446d5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="Re2da6383978b4e5a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="Rbbad923c6401491d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="R93cf3453a8614827"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="R956365ee4a0d4c6d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="R529b721da30c4ebb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="R3f5ce2787daa45ff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="R966f83d6dbe74510"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="R4c9f68b446a14797"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="R53f4107219b14887"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="R3be033f8c5b84e89"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="R7901d76c09054618"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="R212c237b5738477e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="R76959316366b4565"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="Rd958ee3c772d4832"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="R0bcd929ba0ef4e6d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="Red781ed410654bc7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="R547c5183d894416b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="R1a2d02a23bca448c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="Rd373631155de4af6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="R83e2a804f3214e4a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="R86ef5d9548dc4e42"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="R264768f967d94138"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="R235cc69129bd4178"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="R7f0f53c73dfc49ca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="R543074148aa449e9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="Rbabe274fbe7d4763"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="Rb0e0d9d083d24010"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -4252,7 +4252,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb749c89af65049f0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf6904bec54c84ee5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4906,7 +4906,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R128f389f357a44c8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R44b544a0591e4222"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5560,7 +5560,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R84b65bfdb09e49cb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R93ed91f8a80147ee"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6214,7 +6214,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R80d906a83e2e45bc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R59f71466ead04db3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6868,7 +6868,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9506d8d6185a402a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R15b675093ba14cf4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7506,7 +7506,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R345802746fcc4e44"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfbd9de055de9404f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7787,7 +7787,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4bae463e51574672"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R087654c017ef4208"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8119,7 +8119,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R799d5f5cd841442b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R07fd6c083b8d4c8f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8400,7 +8400,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf6693a858c554a43"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2eb7c25ca6f24fde"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8895,7 +8895,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcd8c06ff9647497a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R93ccba026af24f38"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9410,7 +9410,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R229d5c8be3d54e97"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R44852f308945422f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10064,7 +10064,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R03c64cdbd2ce4cf9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra59a4110042a410b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10855,7 +10855,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R714704a35c7f4103"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R85708f25eb284224"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11624,7 +11624,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9bbc01f54d9941db"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8fb4333bdef94203"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12262,7 +12262,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3fcb7327c03643a5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbc94ab6c8db3416c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12810,7 +12810,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6cee2ce7fb9c4b5e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re68a331e406849b5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13228,7 +13228,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R54ecc4db11344a67"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re149aeaab7ea4f3e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13969,7 +13969,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfc6920f9dfd5419c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reacc134942674146"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14289,7 +14289,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R368ed9030ac7463c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R69aefb534c4a43b4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16269,7 +16269,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raf4ad0b70324410c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R475608572828437e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17136,7 +17136,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2a2b368e8e9c43ce"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6b7b9938cfb84b82"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17672,7 +17672,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re2ec94900daf43e9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0ccf628d0d2d46f4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18208,7 +18208,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf32b81a9e8214eb4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd8798170ada4479e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18781,7 +18781,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rab651b8ee1ef459c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4bdc346aa3794fb3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -19305,7 +19305,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdd2d556c81e74f7a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1b8cd14b373946ba"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -19959,7 +19959,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9639c82b2f164bd9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbeba8ae088e24a19"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Homeworlds_Production.xlsx
+++ b/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Homeworlds_Production.xlsx
@@ -2,34 +2,34 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R5b68e7d1b8c446d5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="Re2da6383978b4e5a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="Rbbad923c6401491d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="R93cf3453a8614827"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="R956365ee4a0d4c6d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="R529b721da30c4ebb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="R3f5ce2787daa45ff"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="R966f83d6dbe74510"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="R4c9f68b446a14797"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="R53f4107219b14887"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="R3be033f8c5b84e89"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="R7901d76c09054618"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="R212c237b5738477e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="R76959316366b4565"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="Rd958ee3c772d4832"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="R0bcd929ba0ef4e6d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="Red781ed410654bc7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="R547c5183d894416b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="R1a2d02a23bca448c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="Rd373631155de4af6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="R83e2a804f3214e4a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="R86ef5d9548dc4e42"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="R264768f967d94138"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="R235cc69129bd4178"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="R7f0f53c73dfc49ca"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="R543074148aa449e9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="Rbabe274fbe7d4763"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="Rb0e0d9d083d24010"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R2a850f1edc774be9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="R8e2897ef4036444e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="Rb2f6cbf11fc2408f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="R188f42b5ddba4a77"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="Ra8219eaee7584c3e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="Rdfc9f96ce94c42a8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="Rf2c1aa8c28dc4a99"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="R12d1f132f1eb46d7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="R1aac5426d90b4977"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="Rb99088b4880d40a6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="R6770f8c164cc4f3f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="R4f41a64a88bd41db"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="R1004f38904bf414c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="R00a9d1812e4642c8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="Rabf7609a86c04fbf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="R42c10b589f404fe0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="R09c57b47a7564cee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="Rdb478c77da924582"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="Rb6ac0b96ed714568"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="Rb8f9759599164e9c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="Rc487fdede76e4773"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="Rc4f21eb59eba44be"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="R936fbf91ecb64638"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="Rad14ba050a9d4baa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="Rc6e2ce18377643a5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="Rc90d831fad434c0e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="Rb04644a95340453b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="Rf12dfae3a0be4f18"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -4252,7 +4252,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf6904bec54c84ee5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc3f30eb914ea4676"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4906,7 +4906,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R44b544a0591e4222"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd1a6876c42a04c54"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5560,7 +5560,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R93ed91f8a80147ee"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3e0b4400d6754cf9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6214,7 +6214,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R59f71466ead04db3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R47ab68233c6c43eb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6868,7 +6868,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R15b675093ba14cf4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R543f6f47e395449f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7506,7 +7506,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfbd9de055de9404f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R024de059057d4a21"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7787,7 +7787,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R087654c017ef4208"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0b22ebc3ebf54d21"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8119,7 +8119,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R07fd6c083b8d4c8f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc65b043195a24c8d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8400,7 +8400,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2eb7c25ca6f24fde"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R864c7c2a0e8f4d7d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8895,7 +8895,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R93ccba026af24f38"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdb4cf0d37aec4b26"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9410,7 +9410,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R44852f308945422f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbcfa3d003f96493e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10064,7 +10064,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra59a4110042a410b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R38fb4138a9e64260"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10855,7 +10855,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R85708f25eb284224"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R283f52a0a0a849d5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11624,7 +11624,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8fb4333bdef94203"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R91bcb0dab5be43c5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12262,7 +12262,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbc94ab6c8db3416c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdf13fe96cb9941da"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12810,7 +12810,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re68a331e406849b5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb09d290e651e4c9a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13228,7 +13228,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re149aeaab7ea4f3e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf6fe2429d68849f3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13969,7 +13969,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reacc134942674146"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R517544b99a754bbb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14289,7 +14289,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R69aefb534c4a43b4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1b05841fa2184aac"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16269,7 +16269,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R475608572828437e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdac963b153ed498b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17136,7 +17136,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6b7b9938cfb84b82"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf6e4cc3508bb46d1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17672,7 +17672,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0ccf628d0d2d46f4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R26445b25ff7c46b2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18208,7 +18208,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd8798170ada4479e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9219b3d1dc9c4717"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18781,7 +18781,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4bdc346aa3794fb3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rffa6604fe222428f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -19305,7 +19305,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1b8cd14b373946ba"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R81fb67865f294d84"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -19959,7 +19959,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbeba8ae088e24a19"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb32de64a343742e1"/>
   </x:tableParts>
 </x:worksheet>
 </file>